--- a/src/results_template/CEC2020/10Dim.xlsx
+++ b/src/results_template/CEC2020/10Dim.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GtiHub\Repositories\Base-Optimization-Framework\src\results\results_template\CEC2020\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GtiHub\Repositories\Base-Optimization-Framework\src\results_template\CEC2020\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4896E036-0673-4967-A38C-F15376BCA473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB56AB0F-BF99-4FDB-A720-8F01A9A870F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,8 +34,33 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -673,6 +698,9 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -700,14 +728,91 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="29">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -852,11 +957,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="S2:T32" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17" tableBorderDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="S2:T32" totalsRowShown="0" headerRowDxfId="28" dataDxfId="27" tableBorderDxfId="26">
   <autoFilter ref="S2:T32" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Column1" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Column2" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Column1" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Column2" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1196,26 +1301,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+      <c r="O1" s="21"/>
+      <c r="P1" s="21"/>
+      <c r="Q1" s="21"/>
+      <c r="R1" s="21"/>
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1336,7 +1441,7 @@
       </c>
     </row>
     <row r="3" spans="1:36" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="25" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -1366,69 +1471,69 @@
       <c r="T3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="V3" s="7" t="e">
-        <f>_xlfn.RANK.EQ(D3,$D3:$R3,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W3" s="7" t="e">
-        <f>_xlfn.RANK.EQ(E3,$D3:$R3,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="X3" s="7" t="e">
-        <f>_xlfn.RANK.EQ(F3,$D3:$R3,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Y3" s="7" t="e">
-        <f>_xlfn.RANK.EQ(G3,$D3:$R3,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Z3" s="7" t="e">
-        <f>_xlfn.RANK.EQ(H3,$D3:$R3,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AA3" s="7" t="e">
-        <f>_xlfn.RANK.EQ(I3,$D3:$R3,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AB3" s="7" t="e">
-        <f>_xlfn.RANK.EQ(J3,$D3:$R3,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AC3" s="7" t="e">
-        <f>_xlfn.RANK.EQ(K3,$D3:$R3,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AD3" s="7" t="e">
-        <f>_xlfn.RANK.EQ(L3,$D3:$R3,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AE3" s="7" t="e">
-        <f>_xlfn.RANK.EQ(M3,$D3:$R3,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AF3" s="7" t="e">
-        <f>_xlfn.RANK.EQ(N3,$D3:$R3,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AG3" s="7" t="e">
-        <f>_xlfn.RANK.EQ(O3,$D3:$R3,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AH3" s="7" t="e">
-        <f>_xlfn.RANK.EQ(P3,$D3:$R3,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AI3" s="7" t="e">
-        <f>_xlfn.RANK.EQ(Q3,$D3:$R3,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ3" s="7" t="e">
-        <f>_xlfn.RANK.EQ(R3,$D3:$R3,1)</f>
-        <v>#N/A</v>
+      <c r="V3" s="7" t="e" cm="1">
+        <f t="array" ref="V3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(D3,2-INT(LOG10(ABS(D3))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W3" s="7" t="e" cm="1">
+        <f t="array" ref="W3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(E3,2-INT(LOG10(ABS(E3))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X3" s="7" t="e" cm="1">
+        <f t="array" ref="X3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(F3,2-INT(LOG10(ABS(F3))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y3" s="7" t="e" cm="1">
+        <f t="array" ref="Y3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(G3,2-INT(LOG10(ABS(G3))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z3" s="7" t="e" cm="1">
+        <f t="array" ref="Z3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(H3,2-INT(LOG10(ABS(H3))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA3" s="7" t="e" cm="1">
+        <f t="array" ref="AA3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(I3,2-INT(LOG10(ABS(I3))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB3" s="7" t="e" cm="1">
+        <f t="array" ref="AB3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(J3,2-INT(LOG10(ABS(J3))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC3" s="7" t="e" cm="1">
+        <f t="array" ref="AC3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(K3,2-INT(LOG10(ABS(K3))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD3" s="7" t="e" cm="1">
+        <f t="array" ref="AD3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(L3,2-INT(LOG10(ABS(L3))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE3" s="7" t="e" cm="1">
+        <f t="array" ref="AE3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(M3,2-INT(LOG10(ABS(M3))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF3" s="7" t="e" cm="1">
+        <f t="array" ref="AF3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(N3,2-INT(LOG10(ABS(N3))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG3" s="7" t="e" cm="1">
+        <f t="array" ref="AG3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(O3,2-INT(LOG10(ABS(O3))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH3" s="7" t="e" cm="1">
+        <f t="array" ref="AH3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(P3,2-INT(LOG10(ABS(P3))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI3" s="7" t="e" cm="1">
+        <f t="array" ref="AI3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(Q3,2-INT(LOG10(ABS(Q3))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ3" s="7" t="e" cm="1">
+        <f t="array" ref="AJ3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(R3,2-INT(LOG10(ABS(R3))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A4" s="18"/>
+      <c r="A4" s="19"/>
       <c r="B4" s="10" t="s">
         <v>45</v>
       </c>
@@ -1467,7 +1572,7 @@
       <c r="AF4" s="7"/>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A5" s="22"/>
+      <c r="A5" s="23"/>
       <c r="B5" s="5" t="s">
         <v>45</v>
       </c>
@@ -1506,7 +1611,7 @@
       <c r="AF5" s="7"/>
     </row>
     <row r="6" spans="1:36" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="19" t="s">
         <v>18</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -1536,69 +1641,69 @@
       <c r="T6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="V6" s="7" t="e">
-        <f>_xlfn.RANK.EQ(D6,$D6:$R6,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W6" s="7" t="e">
-        <f>_xlfn.RANK.EQ(E6,$D6:$R6,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="X6" s="7" t="e">
-        <f>_xlfn.RANK.EQ(F6,$D6:$R6,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Y6" s="7" t="e">
-        <f>_xlfn.RANK.EQ(G6,$D6:$R6,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Z6" s="7" t="e">
-        <f>_xlfn.RANK.EQ(H6,$D6:$R6,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AA6" s="7" t="e">
-        <f>_xlfn.RANK.EQ(I6,$D6:$R6,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AB6" s="7" t="e">
-        <f>_xlfn.RANK.EQ(J6,$D6:$R6,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AC6" s="7" t="e">
-        <f>_xlfn.RANK.EQ(K6,$D6:$R6,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AD6" s="7" t="e">
-        <f>_xlfn.RANK.EQ(L6,$D6:$R6,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AE6" s="7" t="e">
-        <f>_xlfn.RANK.EQ(M6,$D6:$R6,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AF6" s="7" t="e">
-        <f>_xlfn.RANK.EQ(N6,$D6:$R6,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AG6" s="7" t="e">
-        <f>_xlfn.RANK.EQ(O6,$D6:$R6,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AH6" s="7" t="e">
-        <f>_xlfn.RANK.EQ(P6,$D6:$R6,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AI6" s="7" t="e">
-        <f>_xlfn.RANK.EQ(Q6,$D6:$R6,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ6" s="7" t="e">
-        <f>_xlfn.RANK.EQ(R6,$D6:$R6,1)</f>
-        <v>#N/A</v>
+      <c r="V6" s="7" t="e" cm="1">
+        <f t="array" ref="V6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(D6,2-INT(LOG10(ABS(D6))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W6" s="7" t="e" cm="1">
+        <f t="array" ref="W6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(E6,2-INT(LOG10(ABS(E6))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X6" s="7" t="e" cm="1">
+        <f t="array" ref="X6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(F6,2-INT(LOG10(ABS(F6))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y6" s="7" t="e" cm="1">
+        <f t="array" ref="Y6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(G6,2-INT(LOG10(ABS(G6))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z6" s="7" t="e" cm="1">
+        <f t="array" ref="Z6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(H6,2-INT(LOG10(ABS(H6))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA6" s="7" t="e" cm="1">
+        <f t="array" ref="AA6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(I6,2-INT(LOG10(ABS(I6))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB6" s="7" t="e" cm="1">
+        <f t="array" ref="AB6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(J6,2-INT(LOG10(ABS(J6))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC6" s="7" t="e" cm="1">
+        <f t="array" ref="AC6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(K6,2-INT(LOG10(ABS(K6))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD6" s="7" t="e" cm="1">
+        <f t="array" ref="AD6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(L6,2-INT(LOG10(ABS(L6))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE6" s="7" t="e" cm="1">
+        <f t="array" ref="AE6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(M6,2-INT(LOG10(ABS(M6))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF6" s="7" t="e" cm="1">
+        <f t="array" ref="AF6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(N6,2-INT(LOG10(ABS(N6))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG6" s="7" t="e" cm="1">
+        <f t="array" ref="AG6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(O6,2-INT(LOG10(ABS(O6))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH6" s="7" t="e" cm="1">
+        <f t="array" ref="AH6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(P6,2-INT(LOG10(ABS(P6))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI6" s="7" t="e" cm="1">
+        <f t="array" ref="AI6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(Q6,2-INT(LOG10(ABS(Q6))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ6" s="7" t="e" cm="1">
+        <f t="array" ref="AJ6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(R6,2-INT(LOG10(ABS(R6))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A7" s="18"/>
+      <c r="A7" s="19"/>
       <c r="B7" s="10" t="s">
         <v>46</v>
       </c>
@@ -1637,7 +1742,7 @@
       <c r="AF7" s="7"/>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A8" s="18"/>
+      <c r="A8" s="19"/>
       <c r="B8" s="5" t="s">
         <v>46</v>
       </c>
@@ -1676,7 +1781,7 @@
       <c r="AF8" s="7"/>
     </row>
     <row r="9" spans="1:36" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="18"/>
+      <c r="A9" s="19"/>
       <c r="B9" s="2" t="s">
         <v>47</v>
       </c>
@@ -1704,69 +1809,69 @@
       <c r="T9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="V9" s="7" t="e">
-        <f>_xlfn.RANK.EQ(D9,$D9:$R9,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W9" s="7" t="e">
-        <f>_xlfn.RANK.EQ(E9,$D9:$R9,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="X9" s="7" t="e">
-        <f>_xlfn.RANK.EQ(F9,$D9:$R9,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Y9" s="7" t="e">
-        <f>_xlfn.RANK.EQ(G9,$D9:$R9,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Z9" s="7" t="e">
-        <f>_xlfn.RANK.EQ(H9,$D9:$R9,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AA9" s="7" t="e">
-        <f>_xlfn.RANK.EQ(I9,$D9:$R9,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AB9" s="7" t="e">
-        <f>_xlfn.RANK.EQ(J9,$D9:$R9,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AC9" s="7" t="e">
-        <f>_xlfn.RANK.EQ(K9,$D9:$R9,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AD9" s="7" t="e">
-        <f>_xlfn.RANK.EQ(L9,$D9:$R9,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AE9" s="7" t="e">
-        <f>_xlfn.RANK.EQ(M9,$D9:$R9,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AF9" s="7" t="e">
-        <f>_xlfn.RANK.EQ(N9,$D9:$R9,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AG9" s="7" t="e">
-        <f>_xlfn.RANK.EQ(O9,$D9:$R9,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AH9" s="7" t="e">
-        <f>_xlfn.RANK.EQ(P9,$D9:$R9,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AI9" s="7" t="e">
-        <f>_xlfn.RANK.EQ(Q9,$D9:$R9,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ9" s="7" t="e">
-        <f>_xlfn.RANK.EQ(R9,$D9:$R9,1)</f>
-        <v>#N/A</v>
+      <c r="V9" s="7" t="e" cm="1">
+        <f t="array" ref="V9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(D9,2-INT(LOG10(ABS(D9))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W9" s="7" t="e" cm="1">
+        <f t="array" ref="W9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(E9,2-INT(LOG10(ABS(E9))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X9" s="7" t="e" cm="1">
+        <f t="array" ref="X9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(F9,2-INT(LOG10(ABS(F9))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y9" s="7" t="e" cm="1">
+        <f t="array" ref="Y9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(G9,2-INT(LOG10(ABS(G9))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z9" s="7" t="e" cm="1">
+        <f t="array" ref="Z9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(H9,2-INT(LOG10(ABS(H9))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA9" s="7" t="e" cm="1">
+        <f t="array" ref="AA9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(I9,2-INT(LOG10(ABS(I9))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB9" s="7" t="e" cm="1">
+        <f t="array" ref="AB9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(J9,2-INT(LOG10(ABS(J9))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC9" s="7" t="e" cm="1">
+        <f t="array" ref="AC9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(K9,2-INT(LOG10(ABS(K9))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD9" s="7" t="e" cm="1">
+        <f t="array" ref="AD9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(L9,2-INT(LOG10(ABS(L9))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE9" s="7" t="e" cm="1">
+        <f t="array" ref="AE9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(M9,2-INT(LOG10(ABS(M9))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF9" s="7" t="e" cm="1">
+        <f t="array" ref="AF9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(N9,2-INT(LOG10(ABS(N9))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG9" s="7" t="e" cm="1">
+        <f t="array" ref="AG9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(O9,2-INT(LOG10(ABS(O9))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH9" s="7" t="e" cm="1">
+        <f t="array" ref="AH9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(P9,2-INT(LOG10(ABS(P9))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI9" s="7" t="e" cm="1">
+        <f t="array" ref="AI9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(Q9,2-INT(LOG10(ABS(Q9))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ9" s="7" t="e" cm="1">
+        <f t="array" ref="AJ9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(R9,2-INT(LOG10(ABS(R9))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A10" s="18"/>
+      <c r="A10" s="19"/>
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
@@ -1805,7 +1910,7 @@
       <c r="AF10" s="7"/>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A11" s="18"/>
+      <c r="A11" s="19"/>
       <c r="B11" s="5" t="s">
         <v>47</v>
       </c>
@@ -1844,7 +1949,7 @@
       <c r="AF11" s="7"/>
     </row>
     <row r="12" spans="1:36" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="18"/>
+      <c r="A12" s="19"/>
       <c r="B12" s="2" t="s">
         <v>48</v>
       </c>
@@ -1872,69 +1977,69 @@
       <c r="T12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="V12" s="7" t="e">
-        <f>_xlfn.RANK.EQ(D12,$D12:$R12,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W12" s="7" t="e">
-        <f>_xlfn.RANK.EQ(E12,$D12:$R12,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="X12" s="7" t="e">
-        <f>_xlfn.RANK.EQ(F12,$D12:$R12,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Y12" s="7" t="e">
-        <f>_xlfn.RANK.EQ(G12,$D12:$R12,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Z12" s="7" t="e">
-        <f>_xlfn.RANK.EQ(H12,$D12:$R12,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AA12" s="7" t="e">
-        <f>_xlfn.RANK.EQ(I12,$D12:$R12,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AB12" s="7" t="e">
-        <f>_xlfn.RANK.EQ(J12,$D12:$R12,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AC12" s="7" t="e">
-        <f>_xlfn.RANK.EQ(K12,$D12:$R12,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AD12" s="7" t="e">
-        <f>_xlfn.RANK.EQ(L12,$D12:$R12,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AE12" s="7" t="e">
-        <f>_xlfn.RANK.EQ(M12,$D12:$R12,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AF12" s="7" t="e">
-        <f>_xlfn.RANK.EQ(N12,$D12:$R12,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AG12" s="7" t="e">
-        <f>_xlfn.RANK.EQ(O12,$D12:$R12,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AH12" s="7" t="e">
-        <f>_xlfn.RANK.EQ(P12,$D12:$R12,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AI12" s="7" t="e">
-        <f>_xlfn.RANK.EQ(Q12,$D12:$R12,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ12" s="7" t="e">
-        <f>_xlfn.RANK.EQ(R12,$D12:$R12,1)</f>
-        <v>#N/A</v>
+      <c r="V12" s="7" t="e" cm="1">
+        <f t="array" ref="V12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(D12,2-INT(LOG10(ABS(D12))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W12" s="7" t="e" cm="1">
+        <f t="array" ref="W12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(E12,2-INT(LOG10(ABS(E12))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X12" s="7" t="e" cm="1">
+        <f t="array" ref="X12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(F12,2-INT(LOG10(ABS(F12))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y12" s="7" t="e" cm="1">
+        <f t="array" ref="Y12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(G12,2-INT(LOG10(ABS(G12))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z12" s="7" t="e" cm="1">
+        <f t="array" ref="Z12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(H12,2-INT(LOG10(ABS(H12))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA12" s="7" t="e" cm="1">
+        <f t="array" ref="AA12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(I12,2-INT(LOG10(ABS(I12))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB12" s="7" t="e" cm="1">
+        <f t="array" ref="AB12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(J12,2-INT(LOG10(ABS(J12))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC12" s="7" t="e" cm="1">
+        <f t="array" ref="AC12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(K12,2-INT(LOG10(ABS(K12))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD12" s="7" t="e" cm="1">
+        <f t="array" ref="AD12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(L12,2-INT(LOG10(ABS(L12))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE12" s="7" t="e" cm="1">
+        <f t="array" ref="AE12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(M12,2-INT(LOG10(ABS(M12))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF12" s="7" t="e" cm="1">
+        <f t="array" ref="AF12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(N12,2-INT(LOG10(ABS(N12))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG12" s="7" t="e" cm="1">
+        <f t="array" ref="AG12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(O12,2-INT(LOG10(ABS(O12))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH12" s="7" t="e" cm="1">
+        <f t="array" ref="AH12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(P12,2-INT(LOG10(ABS(P12))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI12" s="7" t="e" cm="1">
+        <f t="array" ref="AI12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(Q12,2-INT(LOG10(ABS(Q12))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ12" s="7" t="e" cm="1">
+        <f t="array" ref="AJ12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(R12,2-INT(LOG10(ABS(R12))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A13" s="18"/>
+      <c r="A13" s="19"/>
       <c r="B13" s="10" t="s">
         <v>48</v>
       </c>
@@ -1973,7 +2078,7 @@
       <c r="AF13" s="7"/>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A14" s="22"/>
+      <c r="A14" s="23"/>
       <c r="B14" s="5" t="s">
         <v>48</v>
       </c>
@@ -2012,7 +2117,7 @@
       <c r="AF14" s="7"/>
     </row>
     <row r="15" spans="1:36" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="19" t="s">
         <v>17</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -2042,69 +2147,69 @@
       <c r="T15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="V15" s="7" t="e">
-        <f>_xlfn.RANK.EQ(D15,$D15:$R15,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W15" s="7" t="e">
-        <f>_xlfn.RANK.EQ(E15,$D15:$R15,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="X15" s="7" t="e">
-        <f>_xlfn.RANK.EQ(F15,$D15:$R15,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Y15" s="7" t="e">
-        <f>_xlfn.RANK.EQ(G15,$D15:$R15,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Z15" s="7" t="e">
-        <f>_xlfn.RANK.EQ(H15,$D15:$R15,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AA15" s="7" t="e">
-        <f>_xlfn.RANK.EQ(I15,$D15:$R15,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AB15" s="7" t="e">
-        <f>_xlfn.RANK.EQ(J15,$D15:$R15,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AC15" s="7" t="e">
-        <f>_xlfn.RANK.EQ(K15,$D15:$R15,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AD15" s="7" t="e">
-        <f>_xlfn.RANK.EQ(L15,$D15:$R15,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AE15" s="7" t="e">
-        <f>_xlfn.RANK.EQ(M15,$D15:$R15,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AF15" s="7" t="e">
-        <f>_xlfn.RANK.EQ(N15,$D15:$R15,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AG15" s="7" t="e">
-        <f>_xlfn.RANK.EQ(O15,$D15:$R15,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AH15" s="7" t="e">
-        <f>_xlfn.RANK.EQ(P15,$D15:$R15,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AI15" s="7" t="e">
-        <f>_xlfn.RANK.EQ(Q15,$D15:$R15,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ15" s="7" t="e">
-        <f>_xlfn.RANK.EQ(R15,$D15:$R15,1)</f>
-        <v>#N/A</v>
+      <c r="V15" s="7" t="e" cm="1">
+        <f t="array" ref="V15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(D15,2-INT(LOG10(ABS(D15))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W15" s="7" t="e" cm="1">
+        <f t="array" ref="W15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(E15,2-INT(LOG10(ABS(E15))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X15" s="7" t="e" cm="1">
+        <f t="array" ref="X15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(F15,2-INT(LOG10(ABS(F15))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y15" s="7" t="e" cm="1">
+        <f t="array" ref="Y15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(G15,2-INT(LOG10(ABS(G15))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z15" s="7" t="e" cm="1">
+        <f t="array" ref="Z15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(H15,2-INT(LOG10(ABS(H15))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA15" s="7" t="e" cm="1">
+        <f t="array" ref="AA15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(I15,2-INT(LOG10(ABS(I15))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB15" s="7" t="e" cm="1">
+        <f t="array" ref="AB15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(J15,2-INT(LOG10(ABS(J15))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC15" s="7" t="e" cm="1">
+        <f t="array" ref="AC15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(K15,2-INT(LOG10(ABS(K15))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD15" s="7" t="e" cm="1">
+        <f t="array" ref="AD15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(L15,2-INT(LOG10(ABS(L15))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE15" s="7" t="e" cm="1">
+        <f t="array" ref="AE15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(M15,2-INT(LOG10(ABS(M15))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF15" s="7" t="e" cm="1">
+        <f t="array" ref="AF15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(N15,2-INT(LOG10(ABS(N15))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG15" s="7" t="e" cm="1">
+        <f t="array" ref="AG15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(O15,2-INT(LOG10(ABS(O15))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH15" s="7" t="e" cm="1">
+        <f t="array" ref="AH15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(P15,2-INT(LOG10(ABS(P15))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI15" s="7" t="e" cm="1">
+        <f t="array" ref="AI15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(Q15,2-INT(LOG10(ABS(Q15))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ15" s="7" t="e" cm="1">
+        <f t="array" ref="AJ15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(R15,2-INT(LOG10(ABS(R15))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A16" s="18"/>
+      <c r="A16" s="19"/>
       <c r="B16" s="10" t="s">
         <v>49</v>
       </c>
@@ -2143,7 +2248,7 @@
       <c r="AF16" s="7"/>
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A17" s="18"/>
+      <c r="A17" s="19"/>
       <c r="B17" s="5" t="s">
         <v>49</v>
       </c>
@@ -2182,7 +2287,7 @@
       <c r="AF17" s="7"/>
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A18" s="18"/>
+      <c r="A18" s="19"/>
       <c r="B18" s="2" t="s">
         <v>50</v>
       </c>
@@ -2210,69 +2315,69 @@
       <c r="T18" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="V18" s="7" t="e">
-        <f>_xlfn.RANK.EQ(D18,$D18:$R18,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W18" s="7" t="e">
-        <f>_xlfn.RANK.EQ(E18,$D18:$R18,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="X18" s="7" t="e">
-        <f>_xlfn.RANK.EQ(F18,$D18:$R18,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Y18" s="7" t="e">
-        <f>_xlfn.RANK.EQ(G18,$D18:$R18,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Z18" s="7" t="e">
-        <f>_xlfn.RANK.EQ(H18,$D18:$R18,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AA18" s="7" t="e">
-        <f>_xlfn.RANK.EQ(I18,$D18:$R18,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AB18" s="7" t="e">
-        <f>_xlfn.RANK.EQ(J18,$D18:$R18,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AC18" s="7" t="e">
-        <f>_xlfn.RANK.EQ(K18,$D18:$R18,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AD18" s="7" t="e">
-        <f>_xlfn.RANK.EQ(L18,$D18:$R18,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AE18" s="7" t="e">
-        <f>_xlfn.RANK.EQ(M18,$D18:$R18,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AF18" s="7" t="e">
-        <f>_xlfn.RANK.EQ(N18,$D18:$R18,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AG18" s="7" t="e">
-        <f>_xlfn.RANK.EQ(O18,$D18:$R18,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AH18" s="7" t="e">
-        <f>_xlfn.RANK.EQ(P18,$D18:$R18,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AI18" s="7" t="e">
-        <f>_xlfn.RANK.EQ(Q18,$D18:$R18,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ18" s="7" t="e">
-        <f>_xlfn.RANK.EQ(R18,$D18:$R18,1)</f>
-        <v>#N/A</v>
+      <c r="V18" s="7" t="e" cm="1">
+        <f t="array" ref="V18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(D18,2-INT(LOG10(ABS(D18))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W18" s="7" t="e" cm="1">
+        <f t="array" ref="W18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(E18,2-INT(LOG10(ABS(E18))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X18" s="7" t="e" cm="1">
+        <f t="array" ref="X18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(F18,2-INT(LOG10(ABS(F18))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y18" s="7" t="e" cm="1">
+        <f t="array" ref="Y18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(G18,2-INT(LOG10(ABS(G18))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z18" s="7" t="e" cm="1">
+        <f t="array" ref="Z18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(H18,2-INT(LOG10(ABS(H18))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA18" s="7" t="e" cm="1">
+        <f t="array" ref="AA18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(I18,2-INT(LOG10(ABS(I18))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB18" s="7" t="e" cm="1">
+        <f t="array" ref="AB18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(J18,2-INT(LOG10(ABS(J18))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC18" s="7" t="e" cm="1">
+        <f t="array" ref="AC18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(K18,2-INT(LOG10(ABS(K18))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD18" s="7" t="e" cm="1">
+        <f t="array" ref="AD18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(L18,2-INT(LOG10(ABS(L18))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE18" s="7" t="e" cm="1">
+        <f t="array" ref="AE18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(M18,2-INT(LOG10(ABS(M18))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF18" s="7" t="e" cm="1">
+        <f t="array" ref="AF18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(N18,2-INT(LOG10(ABS(N18))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG18" s="7" t="e" cm="1">
+        <f t="array" ref="AG18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(O18,2-INT(LOG10(ABS(O18))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH18" s="7" t="e" cm="1">
+        <f t="array" ref="AH18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(P18,2-INT(LOG10(ABS(P18))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI18" s="7" t="e" cm="1">
+        <f t="array" ref="AI18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(Q18,2-INT(LOG10(ABS(Q18))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ18" s="7" t="e" cm="1">
+        <f t="array" ref="AJ18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(R18,2-INT(LOG10(ABS(R18))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="19" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A19" s="18"/>
+      <c r="A19" s="19"/>
       <c r="B19" s="10" t="s">
         <v>50</v>
       </c>
@@ -2311,7 +2416,7 @@
       <c r="AF19" s="7"/>
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A20" s="18"/>
+      <c r="A20" s="19"/>
       <c r="B20" s="5" t="s">
         <v>50</v>
       </c>
@@ -2350,7 +2455,7 @@
       <c r="AF20" s="7"/>
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A21" s="18"/>
+      <c r="A21" s="19"/>
       <c r="B21" s="2" t="s">
         <v>51</v>
       </c>
@@ -2378,69 +2483,69 @@
       <c r="T21" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="V21" s="7" t="e">
-        <f>_xlfn.RANK.EQ(D21,$D21:$R21,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W21" s="7" t="e">
-        <f>_xlfn.RANK.EQ(E21,$D21:$R21,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="X21" s="7" t="e">
-        <f>_xlfn.RANK.EQ(F21,$D21:$R21,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Y21" s="7" t="e">
-        <f>_xlfn.RANK.EQ(G21,$D21:$R21,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Z21" s="7" t="e">
-        <f>_xlfn.RANK.EQ(H21,$D21:$R21,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AA21" s="7" t="e">
-        <f>_xlfn.RANK.EQ(I21,$D21:$R21,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AB21" s="7" t="e">
-        <f>_xlfn.RANK.EQ(J21,$D21:$R21,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AC21" s="7" t="e">
-        <f>_xlfn.RANK.EQ(K21,$D21:$R21,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AD21" s="7" t="e">
-        <f>_xlfn.RANK.EQ(L21,$D21:$R21,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AE21" s="7" t="e">
-        <f>_xlfn.RANK.EQ(M21,$D21:$R21,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AF21" s="7" t="e">
-        <f>_xlfn.RANK.EQ(N21,$D21:$R21,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AG21" s="7" t="e">
-        <f>_xlfn.RANK.EQ(O21,$D21:$R21,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AH21" s="7" t="e">
-        <f>_xlfn.RANK.EQ(P21,$D21:$R21,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AI21" s="7" t="e">
-        <f>_xlfn.RANK.EQ(Q21,$D21:$R21,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ21" s="7" t="e">
-        <f>_xlfn.RANK.EQ(R21,$D21:$R21,1)</f>
-        <v>#N/A</v>
+      <c r="V21" s="7" t="e" cm="1">
+        <f t="array" ref="V21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(D21,2-INT(LOG10(ABS(D21))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W21" s="7" t="e" cm="1">
+        <f t="array" ref="W21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(E21,2-INT(LOG10(ABS(E21))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X21" s="7" t="e" cm="1">
+        <f t="array" ref="X21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(F21,2-INT(LOG10(ABS(F21))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y21" s="7" t="e" cm="1">
+        <f t="array" ref="Y21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(G21,2-INT(LOG10(ABS(G21))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z21" s="7" t="e" cm="1">
+        <f t="array" ref="Z21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(H21,2-INT(LOG10(ABS(H21))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA21" s="7" t="e" cm="1">
+        <f t="array" ref="AA21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(I21,2-INT(LOG10(ABS(I21))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB21" s="7" t="e" cm="1">
+        <f t="array" ref="AB21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(J21,2-INT(LOG10(ABS(J21))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC21" s="7" t="e" cm="1">
+        <f t="array" ref="AC21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(K21,2-INT(LOG10(ABS(K21))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD21" s="7" t="e" cm="1">
+        <f t="array" ref="AD21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(L21,2-INT(LOG10(ABS(L21))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE21" s="7" t="e" cm="1">
+        <f t="array" ref="AE21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(M21,2-INT(LOG10(ABS(M21))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF21" s="7" t="e" cm="1">
+        <f t="array" ref="AF21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(N21,2-INT(LOG10(ABS(N21))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG21" s="7" t="e" cm="1">
+        <f t="array" ref="AG21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(O21,2-INT(LOG10(ABS(O21))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH21" s="7" t="e" cm="1">
+        <f t="array" ref="AH21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(P21,2-INT(LOG10(ABS(P21))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI21" s="7" t="e" cm="1">
+        <f t="array" ref="AI21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(Q21,2-INT(LOG10(ABS(Q21))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ21" s="7" t="e" cm="1">
+        <f t="array" ref="AJ21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(R21,2-INT(LOG10(ABS(R21))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A22" s="18"/>
+      <c r="A22" s="19"/>
       <c r="B22" s="10" t="s">
         <v>51</v>
       </c>
@@ -2479,7 +2584,7 @@
       <c r="AF22" s="7"/>
     </row>
     <row r="23" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A23" s="22"/>
+      <c r="A23" s="23"/>
       <c r="B23" s="5" t="s">
         <v>51</v>
       </c>
@@ -2518,7 +2623,7 @@
       <c r="AF23" s="7"/>
     </row>
     <row r="24" spans="1:36" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="18" t="s">
+      <c r="A24" s="19" t="s">
         <v>19</v>
       </c>
       <c r="B24" s="2" t="s">
@@ -2548,69 +2653,69 @@
       <c r="T24" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="V24" s="7" t="e">
-        <f>_xlfn.RANK.EQ(D24,$D24:$R24,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W24" s="7" t="e">
-        <f>_xlfn.RANK.EQ(E24,$D24:$R24,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="X24" s="7" t="e">
-        <f>_xlfn.RANK.EQ(F24,$D24:$R24,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Y24" s="7" t="e">
-        <f>_xlfn.RANK.EQ(G24,$D24:$R24,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Z24" s="7" t="e">
-        <f>_xlfn.RANK.EQ(H24,$D24:$R24,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AA24" s="7" t="e">
-        <f>_xlfn.RANK.EQ(I24,$D24:$R24,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AB24" s="7" t="e">
-        <f>_xlfn.RANK.EQ(J24,$D24:$R24,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AC24" s="7" t="e">
-        <f>_xlfn.RANK.EQ(K24,$D24:$R24,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AD24" s="7" t="e">
-        <f>_xlfn.RANK.EQ(L24,$D24:$R24,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AE24" s="7" t="e">
-        <f>_xlfn.RANK.EQ(M24,$D24:$R24,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AF24" s="7" t="e">
-        <f>_xlfn.RANK.EQ(N24,$D24:$R24,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AG24" s="7" t="e">
-        <f>_xlfn.RANK.EQ(O24,$D24:$R24,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AH24" s="7" t="e">
-        <f>_xlfn.RANK.EQ(P24,$D24:$R24,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AI24" s="7" t="e">
-        <f>_xlfn.RANK.EQ(Q24,$D24:$R24,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ24" s="7" t="e">
-        <f>_xlfn.RANK.EQ(R24,$D24:$R24,1)</f>
-        <v>#N/A</v>
+      <c r="V24" s="7" t="e" cm="1">
+        <f t="array" ref="V24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(D24,2-INT(LOG10(ABS(D24))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W24" s="7" t="e" cm="1">
+        <f t="array" ref="W24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(E24,2-INT(LOG10(ABS(E24))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X24" s="7" t="e" cm="1">
+        <f t="array" ref="X24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(F24,2-INT(LOG10(ABS(F24))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y24" s="7" t="e" cm="1">
+        <f t="array" ref="Y24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(G24,2-INT(LOG10(ABS(G24))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z24" s="7" t="e" cm="1">
+        <f t="array" ref="Z24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(H24,2-INT(LOG10(ABS(H24))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA24" s="7" t="e" cm="1">
+        <f t="array" ref="AA24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(I24,2-INT(LOG10(ABS(I24))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB24" s="7" t="e" cm="1">
+        <f t="array" ref="AB24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(J24,2-INT(LOG10(ABS(J24))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC24" s="7" t="e" cm="1">
+        <f t="array" ref="AC24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(K24,2-INT(LOG10(ABS(K24))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD24" s="7" t="e" cm="1">
+        <f t="array" ref="AD24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(L24,2-INT(LOG10(ABS(L24))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE24" s="7" t="e" cm="1">
+        <f t="array" ref="AE24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(M24,2-INT(LOG10(ABS(M24))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF24" s="7" t="e" cm="1">
+        <f t="array" ref="AF24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(N24,2-INT(LOG10(ABS(N24))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG24" s="7" t="e" cm="1">
+        <f t="array" ref="AG24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(O24,2-INT(LOG10(ABS(O24))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH24" s="7" t="e" cm="1">
+        <f t="array" ref="AH24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(P24,2-INT(LOG10(ABS(P24))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI24" s="7" t="e" cm="1">
+        <f t="array" ref="AI24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(Q24,2-INT(LOG10(ABS(Q24))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ24" s="7" t="e" cm="1">
+        <f t="array" ref="AJ24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(R24,2-INT(LOG10(ABS(R24))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A25" s="18"/>
+      <c r="A25" s="19"/>
       <c r="B25" s="10" t="s">
         <v>52</v>
       </c>
@@ -2649,7 +2754,7 @@
       <c r="AF25" s="7"/>
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A26" s="18"/>
+      <c r="A26" s="19"/>
       <c r="B26" s="5" t="s">
         <v>52</v>
       </c>
@@ -2688,7 +2793,7 @@
       <c r="AF26" s="7"/>
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A27" s="18"/>
+      <c r="A27" s="19"/>
       <c r="B27" s="2" t="s">
         <v>53</v>
       </c>
@@ -2716,69 +2821,69 @@
       <c r="T27" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="V27" s="7" t="e">
-        <f>_xlfn.RANK.EQ(D27,$D27:$R27,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W27" s="7" t="e">
-        <f>_xlfn.RANK.EQ(E27,$D27:$R27,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="X27" s="7" t="e">
-        <f>_xlfn.RANK.EQ(F27,$D27:$R27,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Y27" s="7" t="e">
-        <f>_xlfn.RANK.EQ(G27,$D27:$R27,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Z27" s="7" t="e">
-        <f>_xlfn.RANK.EQ(H27,$D27:$R27,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AA27" s="7" t="e">
-        <f>_xlfn.RANK.EQ(I27,$D27:$R27,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AB27" s="7" t="e">
-        <f>_xlfn.RANK.EQ(J27,$D27:$R27,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AC27" s="7" t="e">
-        <f>_xlfn.RANK.EQ(K27,$D27:$R27,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AD27" s="7" t="e">
-        <f>_xlfn.RANK.EQ(L27,$D27:$R27,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AE27" s="7" t="e">
-        <f>_xlfn.RANK.EQ(M27,$D27:$R27,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AF27" s="7" t="e">
-        <f>_xlfn.RANK.EQ(N27,$D27:$R27,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AG27" s="7" t="e">
-        <f>_xlfn.RANK.EQ(O27,$D27:$R27,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AH27" s="7" t="e">
-        <f>_xlfn.RANK.EQ(P27,$D27:$R27,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AI27" s="7" t="e">
-        <f>_xlfn.RANK.EQ(Q27,$D27:$R27,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ27" s="7" t="e">
-        <f>_xlfn.RANK.EQ(R27,$D27:$R27,1)</f>
-        <v>#N/A</v>
+      <c r="V27" s="7" t="e" cm="1">
+        <f t="array" ref="V27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(D27,2-INT(LOG10(ABS(D27))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W27" s="7" t="e" cm="1">
+        <f t="array" ref="W27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(E27,2-INT(LOG10(ABS(E27))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X27" s="7" t="e" cm="1">
+        <f t="array" ref="X27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(F27,2-INT(LOG10(ABS(F27))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y27" s="7" t="e" cm="1">
+        <f t="array" ref="Y27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(G27,2-INT(LOG10(ABS(G27))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z27" s="7" t="e" cm="1">
+        <f t="array" ref="Z27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(H27,2-INT(LOG10(ABS(H27))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA27" s="7" t="e" cm="1">
+        <f t="array" ref="AA27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(I27,2-INT(LOG10(ABS(I27))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB27" s="7" t="e" cm="1">
+        <f t="array" ref="AB27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(J27,2-INT(LOG10(ABS(J27))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC27" s="7" t="e" cm="1">
+        <f t="array" ref="AC27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(K27,2-INT(LOG10(ABS(K27))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD27" s="7" t="e" cm="1">
+        <f t="array" ref="AD27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(L27,2-INT(LOG10(ABS(L27))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE27" s="7" t="e" cm="1">
+        <f t="array" ref="AE27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(M27,2-INT(LOG10(ABS(M27))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF27" s="7" t="e" cm="1">
+        <f t="array" ref="AF27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(N27,2-INT(LOG10(ABS(N27))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG27" s="7" t="e" cm="1">
+        <f t="array" ref="AG27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(O27,2-INT(LOG10(ABS(O27))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH27" s="7" t="e" cm="1">
+        <f t="array" ref="AH27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(P27,2-INT(LOG10(ABS(P27))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI27" s="7" t="e" cm="1">
+        <f t="array" ref="AI27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(Q27,2-INT(LOG10(ABS(Q27))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ27" s="7" t="e" cm="1">
+        <f t="array" ref="AJ27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(R27,2-INT(LOG10(ABS(R27))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="28" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A28" s="18"/>
+      <c r="A28" s="19"/>
       <c r="B28" s="10" t="s">
         <v>53</v>
       </c>
@@ -2817,7 +2922,7 @@
       <c r="AF28" s="7"/>
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A29" s="18"/>
+      <c r="A29" s="19"/>
       <c r="B29" s="5" t="s">
         <v>53</v>
       </c>
@@ -2856,7 +2961,7 @@
       <c r="AF29" s="7"/>
     </row>
     <row r="30" spans="1:36" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="18"/>
+      <c r="A30" s="19"/>
       <c r="B30" s="2" t="s">
         <v>54</v>
       </c>
@@ -2884,69 +2989,69 @@
       <c r="T30" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="V30" s="7" t="e">
-        <f>_xlfn.RANK.EQ(D30,$D30:$R30,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="W30" s="7" t="e">
-        <f>_xlfn.RANK.EQ(E30,$D30:$R30,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="X30" s="7" t="e">
-        <f>_xlfn.RANK.EQ(F30,$D30:$R30,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Y30" s="7" t="e">
-        <f>_xlfn.RANK.EQ(G30,$D30:$R30,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Z30" s="7" t="e">
-        <f>_xlfn.RANK.EQ(H30,$D30:$R30,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AA30" s="7" t="e">
-        <f>_xlfn.RANK.EQ(I30,$D30:$R30,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AB30" s="7" t="e">
-        <f>_xlfn.RANK.EQ(J30,$D30:$R30,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AC30" s="7" t="e">
-        <f>_xlfn.RANK.EQ(K30,$D30:$R30,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AD30" s="7" t="e">
-        <f>_xlfn.RANK.EQ(L30,$D30:$R30,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AE30" s="7" t="e">
-        <f>_xlfn.RANK.EQ(M30,$D30:$R30,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AF30" s="7" t="e">
-        <f>_xlfn.RANK.EQ(N30,$D30:$R30,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AG30" s="7" t="e">
-        <f>_xlfn.RANK.EQ(O30,$D30:$R30,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AH30" s="7" t="e">
-        <f>_xlfn.RANK.EQ(P30,$D30:$R30,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AI30" s="7" t="e">
-        <f>_xlfn.RANK.EQ(Q30,$D30:$R30,1)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ30" s="7" t="e">
-        <f>_xlfn.RANK.EQ(R30,$D30:$R30,1)</f>
-        <v>#N/A</v>
+      <c r="V30" s="7" t="e" cm="1">
+        <f t="array" ref="V30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(D30,2-INT(LOG10(ABS(D30))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="W30" s="7" t="e" cm="1">
+        <f t="array" ref="W30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(E30,2-INT(LOG10(ABS(E30))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="X30" s="7" t="e" cm="1">
+        <f t="array" ref="X30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(F30,2-INT(LOG10(ABS(F30))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Y30" s="7" t="e" cm="1">
+        <f t="array" ref="Y30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(G30,2-INT(LOG10(ABS(G30))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="Z30" s="7" t="e" cm="1">
+        <f t="array" ref="Z30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(H30,2-INT(LOG10(ABS(H30))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AA30" s="7" t="e" cm="1">
+        <f t="array" ref="AA30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(I30,2-INT(LOG10(ABS(I30))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AB30" s="7" t="e" cm="1">
+        <f t="array" ref="AB30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(J30,2-INT(LOG10(ABS(J30))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AC30" s="7" t="e" cm="1">
+        <f t="array" ref="AC30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(K30,2-INT(LOG10(ABS(K30))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD30" s="7" t="e" cm="1">
+        <f t="array" ref="AD30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(L30,2-INT(LOG10(ABS(L30))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE30" s="7" t="e" cm="1">
+        <f t="array" ref="AE30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(M30,2-INT(LOG10(ABS(M30))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AF30" s="7" t="e" cm="1">
+        <f t="array" ref="AF30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(N30,2-INT(LOG10(ABS(N30))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AG30" s="7" t="e" cm="1">
+        <f t="array" ref="AG30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(O30,2-INT(LOG10(ABS(O30))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AH30" s="7" t="e" cm="1">
+        <f t="array" ref="AH30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(P30,2-INT(LOG10(ABS(P30))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI30" s="7" t="e" cm="1">
+        <f t="array" ref="AI30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(Q30,2-INT(LOG10(ABS(Q30))))))+1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ30" s="7" t="e" cm="1">
+        <f t="array" ref="AJ30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(R30,2-INT(LOG10(ABS(R30))))))+1</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A31" s="18"/>
+      <c r="A31" s="19"/>
       <c r="B31" s="10" t="s">
         <v>54</v>
       </c>
@@ -2985,7 +3090,7 @@
       <c r="AF31" s="7"/>
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A32" s="22"/>
+      <c r="A32" s="23"/>
       <c r="B32" s="5" t="s">
         <v>54</v>
       </c>
@@ -3024,11 +3129,11 @@
       <c r="AF32" s="7"/>
     </row>
     <row r="33" spans="1:32" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="24" t="s">
+      <c r="A33" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="25"/>
-      <c r="C33" s="25"/>
+      <c r="B33" s="26"/>
+      <c r="C33" s="26"/>
       <c r="D33" s="7">
         <f>COUNTIF(V3:V32,1)</f>
         <v>0</v>
@@ -3102,11 +3207,11 @@
       <c r="AF33" s="7"/>
     </row>
     <row r="34" spans="1:32" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="18" t="s">
+      <c r="A34" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
       <c r="D34" s="7">
         <f>_xlfn.RANK.EQ(D33,$D33:$R33,0)</f>
         <v>1</v>
@@ -3180,70 +3285,70 @@
       <c r="AF34" s="7"/>
     </row>
     <row r="35" spans="1:32" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
+      <c r="A35" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="B35" s="19"/>
-      <c r="C35" s="19"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
       <c r="D35" s="8" t="e">
         <f>AVERAGE(V3:V32)</f>
-        <v>#N/A</v>
+        <v>#NUM!</v>
       </c>
       <c r="E35" s="8" t="e">
         <f t="shared" ref="E35:R35" si="3">AVERAGE(W3:W32)</f>
-        <v>#N/A</v>
+        <v>#NUM!</v>
       </c>
       <c r="F35" s="8" t="e">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>#NUM!</v>
       </c>
       <c r="G35" s="8" t="e">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>#NUM!</v>
       </c>
       <c r="H35" s="8" t="e">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>#NUM!</v>
       </c>
       <c r="I35" s="8" t="e">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>#NUM!</v>
       </c>
       <c r="J35" s="8" t="e">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>#NUM!</v>
       </c>
       <c r="K35" s="8" t="e">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>#NUM!</v>
       </c>
       <c r="L35" s="8" t="e">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>#NUM!</v>
       </c>
       <c r="M35" s="8" t="e">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>#NUM!</v>
       </c>
       <c r="N35" s="8" t="e">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>#NUM!</v>
       </c>
       <c r="O35" s="8" t="e">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>#NUM!</v>
       </c>
       <c r="P35" s="8" t="e">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>#NUM!</v>
       </c>
       <c r="Q35" s="8" t="e">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>#NUM!</v>
       </c>
       <c r="R35" s="8" t="e">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>#NUM!</v>
       </c>
       <c r="V35" s="7"/>
       <c r="W35" s="7"/>
@@ -3258,70 +3363,70 @@
       <c r="AF35" s="7"/>
     </row>
     <row r="36" spans="1:32" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="22" t="s">
+      <c r="A36" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="B36" s="23"/>
-      <c r="C36" s="23"/>
+      <c r="B36" s="24"/>
+      <c r="C36" s="24"/>
       <c r="D36" s="5" t="e">
         <f>_xlfn.RANK.EQ(D35,$D35:$R35,1)</f>
-        <v>#N/A</v>
+        <v>#NUM!</v>
       </c>
       <c r="E36" s="5" t="e">
         <f t="shared" ref="E36:R36" si="4">_xlfn.RANK.EQ(E35,$D35:$R35,1)</f>
-        <v>#N/A</v>
+        <v>#NUM!</v>
       </c>
       <c r="F36" s="5" t="e">
         <f t="shared" si="4"/>
-        <v>#N/A</v>
+        <v>#NUM!</v>
       </c>
       <c r="G36" s="5" t="e">
         <f t="shared" si="4"/>
-        <v>#N/A</v>
+        <v>#NUM!</v>
       </c>
       <c r="H36" s="5" t="e">
         <f t="shared" si="4"/>
-        <v>#N/A</v>
+        <v>#NUM!</v>
       </c>
       <c r="I36" s="5" t="e">
         <f t="shared" si="4"/>
-        <v>#N/A</v>
+        <v>#NUM!</v>
       </c>
       <c r="J36" s="5" t="e">
         <f t="shared" si="4"/>
-        <v>#N/A</v>
+        <v>#NUM!</v>
       </c>
       <c r="K36" s="5" t="e">
         <f t="shared" si="4"/>
-        <v>#N/A</v>
+        <v>#NUM!</v>
       </c>
       <c r="L36" s="5" t="e">
         <f t="shared" si="4"/>
-        <v>#N/A</v>
+        <v>#NUM!</v>
       </c>
       <c r="M36" s="5" t="e">
         <f t="shared" si="4"/>
-        <v>#N/A</v>
+        <v>#NUM!</v>
       </c>
       <c r="N36" s="5" t="e">
         <f t="shared" si="4"/>
-        <v>#N/A</v>
+        <v>#NUM!</v>
       </c>
       <c r="O36" s="5" t="e">
         <f t="shared" si="4"/>
-        <v>#N/A</v>
+        <v>#NUM!</v>
       </c>
       <c r="P36" s="5" t="e">
         <f t="shared" si="4"/>
-        <v>#N/A</v>
+        <v>#NUM!</v>
       </c>
       <c r="Q36" s="5" t="e">
         <f t="shared" si="4"/>
-        <v>#N/A</v>
+        <v>#NUM!</v>
       </c>
       <c r="R36" s="5" t="e">
         <f t="shared" si="4"/>
-        <v>#N/A</v>
+        <v>#NUM!</v>
       </c>
       <c r="V36" s="7"/>
       <c r="W36" s="7"/>
@@ -3427,34 +3532,54 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="D3:R3">
-    <cfRule type="top10" dxfId="13" priority="10" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="9" priority="10">
+      <formula>ROUND(D3,2-INT(LOG10(ABS(D3))))= ROUND(MIN($D3:$R3),2-INT(LOG10(ABS(MIN($D3:$R3)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6:R6">
-    <cfRule type="top10" dxfId="12" priority="9" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="8" priority="9">
+      <formula>ROUND(D6,2-INT(LOG10(ABS(D6))))= ROUND(MIN($D6:$R6),2-INT(LOG10(ABS(MIN($D6:$R6)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:R9">
-    <cfRule type="top10" dxfId="11" priority="8" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="7" priority="8">
+      <formula>ROUND(D9,2-INT(LOG10(ABS(D9))))= ROUND(MIN($D9:$R9),2-INT(LOG10(ABS(MIN($D9:$R9)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D12:R12">
-    <cfRule type="top10" dxfId="10" priority="7" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="6" priority="7">
+      <formula>ROUND(D12,2-INT(LOG10(ABS(D12))))= ROUND(MIN($D12:$R12),2-INT(LOG10(ABS(MIN($D12:$R12)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D15:R15">
-    <cfRule type="top10" dxfId="9" priority="6" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="5" priority="6">
+      <formula>ROUND(D15,2-INT(LOG10(ABS(D15))))= ROUND(MIN($D15:$R15),2-INT(LOG10(ABS(MIN($D15:$R15)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D18:R18">
-    <cfRule type="top10" dxfId="8" priority="5" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="4" priority="5">
+      <formula>ROUND(D18,2-INT(LOG10(ABS(D18))))= ROUND(MIN($D18:$R18),2-INT(LOG10(ABS(MIN($D18:$R18)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D21:R21">
-    <cfRule type="top10" dxfId="7" priority="4" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>ROUND(D21,2-INT(LOG10(ABS(D21))))= ROUND(MIN($D21:$R21),2-INT(LOG10(ABS(MIN($D21:$R21)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D24:R24">
-    <cfRule type="top10" dxfId="6" priority="3" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>ROUND(D24,2-INT(LOG10(ABS(D24))))= ROUND(MIN($D24:$R24),2-INT(LOG10(ABS(MIN($D24:$R24)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D27:R27">
-    <cfRule type="top10" dxfId="5" priority="2" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>ROUND(D27,2-INT(LOG10(ABS(D27))))= ROUND(MIN($D27:$R27),2-INT(LOG10(ABS(MIN($D27:$R27)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D30:R30">
-    <cfRule type="top10" dxfId="4" priority="1" bottom="1" rank="1"/>
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>ROUND(D30,2-INT(LOG10(ABS(D30))))= ROUND(MIN($D30:$R30),2-INT(LOG10(ABS(MIN($D30:$R30)))))</formula>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -3474,68 +3599,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="D2" s="27" t="s">
+      <c r="D2" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="F2" s="27" t="s">
+      <c r="F2" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="G2" s="27" t="s">
+      <c r="G2" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="H2" s="27" t="s">
+      <c r="H2" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="I2" s="27" t="s">
+      <c r="I2" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="J2" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="K2" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="L2" s="27" t="s">
+      <c r="L2" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="M2" s="27" t="s">
+      <c r="M2" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="N2" s="27" t="s">
+      <c r="N2" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="O2" s="27" t="s">
+      <c r="O2" s="18" t="s">
         <v>158</v>
       </c>
     </row>
@@ -3734,7 +3859,7 @@
     <mergeCell ref="A1:O1"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:O12">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="greaterThan">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3753,68 +3878,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="D2" s="27" t="s">
+      <c r="D2" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="F2" s="27" t="s">
+      <c r="F2" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="G2" s="27" t="s">
+      <c r="G2" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="H2" s="27" t="s">
+      <c r="H2" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="I2" s="27" t="s">
+      <c r="I2" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="J2" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="K2" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="L2" s="27" t="s">
+      <c r="L2" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="M2" s="27" t="s">
+      <c r="M2" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="N2" s="27" t="s">
+      <c r="N2" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="O2" s="27" t="s">
+      <c r="O2" s="18" t="s">
         <v>158</v>
       </c>
     </row>
@@ -4013,7 +4138,7 @@
     <mergeCell ref="A1:O1"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:O12">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4032,68 +4157,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="D2" s="27" t="s">
+      <c r="D2" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="F2" s="27" t="s">
+      <c r="F2" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="G2" s="27" t="s">
+      <c r="G2" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="H2" s="27" t="s">
+      <c r="H2" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="I2" s="27" t="s">
+      <c r="I2" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="J2" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="K2" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="L2" s="27" t="s">
+      <c r="L2" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="M2" s="27" t="s">
+      <c r="M2" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="N2" s="27" t="s">
+      <c r="N2" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="O2" s="27" t="s">
+      <c r="O2" s="18" t="s">
         <v>158</v>
       </c>
     </row>
@@ -4292,7 +4417,7 @@
     <mergeCell ref="A1:O1"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:O12">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="greaterThan">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4311,68 +4436,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="D2" s="27" t="s">
+      <c r="D2" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="F2" s="27" t="s">
+      <c r="F2" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="G2" s="27" t="s">
+      <c r="G2" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="H2" s="27" t="s">
+      <c r="H2" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="I2" s="27" t="s">
+      <c r="I2" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="J2" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="K2" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="L2" s="27" t="s">
+      <c r="L2" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="M2" s="27" t="s">
+      <c r="M2" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="N2" s="27" t="s">
+      <c r="N2" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="O2" s="27" t="s">
+      <c r="O2" s="18" t="s">
         <v>158</v>
       </c>
     </row>
@@ -4571,7 +4696,7 @@
     <mergeCell ref="A1:O1"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:O12">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4591,68 +4716,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="D2" s="27" t="s">
+      <c r="D2" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="F2" s="27" t="s">
+      <c r="F2" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="G2" s="27" t="s">
+      <c r="G2" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="H2" s="27" t="s">
+      <c r="H2" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="I2" s="27" t="s">
+      <c r="I2" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="J2" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="K2" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="L2" s="27" t="s">
+      <c r="L2" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="M2" s="27" t="s">
+      <c r="M2" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="N2" s="27" t="s">
+      <c r="N2" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="O2" s="27" t="s">
+      <c r="O2" s="18" t="s">
         <v>158</v>
       </c>
     </row>

--- a/src/results_template/CEC2020/10Dim.xlsx
+++ b/src/results_template/CEC2020/10Dim.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GtiHub\Repositories\Base-Optimization-Framework\src\results_template\CEC2020\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GtiHub\Repositories\Base-Optimization-Framework\src\results\results_template\CEC2020\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB56AB0F-BF99-4FDB-A720-8F01A9A870F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4896E036-0673-4967-A38C-F15376BCA473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,33 +34,8 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -698,9 +673,6 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -728,91 +700,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="29">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u/>
-      </font>
-    </dxf>
+  <dxfs count="19">
     <dxf>
       <font>
         <b/>
@@ -957,11 +852,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="S2:T32" totalsRowShown="0" headerRowDxfId="28" dataDxfId="27" tableBorderDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="S2:T32" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17" tableBorderDxfId="16">
   <autoFilter ref="S2:T32" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Column1" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Column2" dataDxfId="24"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Column1" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Column2" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1301,26 +1196,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="21"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1441,7 +1336,7 @@
       </c>
     </row>
     <row r="3" spans="1:36" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="24" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -1471,69 +1366,69 @@
       <c r="T3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="V3" s="7" t="e" cm="1">
-        <f t="array" ref="V3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(D3,2-INT(LOG10(ABS(D3))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W3" s="7" t="e" cm="1">
-        <f t="array" ref="W3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(E3,2-INT(LOG10(ABS(E3))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X3" s="7" t="e" cm="1">
-        <f t="array" ref="X3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(F3,2-INT(LOG10(ABS(F3))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y3" s="7" t="e" cm="1">
-        <f t="array" ref="Y3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(G3,2-INT(LOG10(ABS(G3))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z3" s="7" t="e" cm="1">
-        <f t="array" ref="Z3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(H3,2-INT(LOG10(ABS(H3))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA3" s="7" t="e" cm="1">
-        <f t="array" ref="AA3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(I3,2-INT(LOG10(ABS(I3))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB3" s="7" t="e" cm="1">
-        <f t="array" ref="AB3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(J3,2-INT(LOG10(ABS(J3))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC3" s="7" t="e" cm="1">
-        <f t="array" ref="AC3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(K3,2-INT(LOG10(ABS(K3))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD3" s="7" t="e" cm="1">
-        <f t="array" ref="AD3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(L3,2-INT(LOG10(ABS(L3))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE3" s="7" t="e" cm="1">
-        <f t="array" ref="AE3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(M3,2-INT(LOG10(ABS(M3))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF3" s="7" t="e" cm="1">
-        <f t="array" ref="AF3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(N3,2-INT(LOG10(ABS(N3))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG3" s="7" t="e" cm="1">
-        <f t="array" ref="AG3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(O3,2-INT(LOG10(ABS(O3))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH3" s="7" t="e" cm="1">
-        <f t="array" ref="AH3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(P3,2-INT(LOG10(ABS(P3))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI3" s="7" t="e" cm="1">
-        <f t="array" ref="AI3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(Q3,2-INT(LOG10(ABS(Q3))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ3" s="7" t="e" cm="1">
-        <f t="array" ref="AJ3">SUMPRODUCT(--(ROUND($D3:$R3,2-INT(LOG10(ABS($D3:$R3))))&lt;ROUND(R3,2-INT(LOG10(ABS(R3))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V3" s="7" t="e">
+        <f>_xlfn.RANK.EQ(D3,$D3:$R3,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W3" s="7" t="e">
+        <f>_xlfn.RANK.EQ(E3,$D3:$R3,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X3" s="7" t="e">
+        <f>_xlfn.RANK.EQ(F3,$D3:$R3,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="Y3" s="7" t="e">
+        <f>_xlfn.RANK.EQ(G3,$D3:$R3,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="Z3" s="7" t="e">
+        <f>_xlfn.RANK.EQ(H3,$D3:$R3,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AA3" s="7" t="e">
+        <f>_xlfn.RANK.EQ(I3,$D3:$R3,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AB3" s="7" t="e">
+        <f>_xlfn.RANK.EQ(J3,$D3:$R3,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AC3" s="7" t="e">
+        <f>_xlfn.RANK.EQ(K3,$D3:$R3,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AD3" s="7" t="e">
+        <f>_xlfn.RANK.EQ(L3,$D3:$R3,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AE3" s="7" t="e">
+        <f>_xlfn.RANK.EQ(M3,$D3:$R3,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF3" s="7" t="e">
+        <f>_xlfn.RANK.EQ(N3,$D3:$R3,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AG3" s="7" t="e">
+        <f>_xlfn.RANK.EQ(O3,$D3:$R3,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AH3" s="7" t="e">
+        <f>_xlfn.RANK.EQ(P3,$D3:$R3,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AI3" s="7" t="e">
+        <f>_xlfn.RANK.EQ(Q3,$D3:$R3,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ3" s="7" t="e">
+        <f>_xlfn.RANK.EQ(R3,$D3:$R3,1)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A4" s="19"/>
+      <c r="A4" s="18"/>
       <c r="B4" s="10" t="s">
         <v>45</v>
       </c>
@@ -1572,7 +1467,7 @@
       <c r="AF4" s="7"/>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A5" s="23"/>
+      <c r="A5" s="22"/>
       <c r="B5" s="5" t="s">
         <v>45</v>
       </c>
@@ -1611,7 +1506,7 @@
       <c r="AF5" s="7"/>
     </row>
     <row r="6" spans="1:36" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>18</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -1641,69 +1536,69 @@
       <c r="T6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="V6" s="7" t="e" cm="1">
-        <f t="array" ref="V6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(D6,2-INT(LOG10(ABS(D6))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W6" s="7" t="e" cm="1">
-        <f t="array" ref="W6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(E6,2-INT(LOG10(ABS(E6))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X6" s="7" t="e" cm="1">
-        <f t="array" ref="X6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(F6,2-INT(LOG10(ABS(F6))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y6" s="7" t="e" cm="1">
-        <f t="array" ref="Y6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(G6,2-INT(LOG10(ABS(G6))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z6" s="7" t="e" cm="1">
-        <f t="array" ref="Z6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(H6,2-INT(LOG10(ABS(H6))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA6" s="7" t="e" cm="1">
-        <f t="array" ref="AA6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(I6,2-INT(LOG10(ABS(I6))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB6" s="7" t="e" cm="1">
-        <f t="array" ref="AB6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(J6,2-INT(LOG10(ABS(J6))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC6" s="7" t="e" cm="1">
-        <f t="array" ref="AC6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(K6,2-INT(LOG10(ABS(K6))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD6" s="7" t="e" cm="1">
-        <f t="array" ref="AD6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(L6,2-INT(LOG10(ABS(L6))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE6" s="7" t="e" cm="1">
-        <f t="array" ref="AE6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(M6,2-INT(LOG10(ABS(M6))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF6" s="7" t="e" cm="1">
-        <f t="array" ref="AF6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(N6,2-INT(LOG10(ABS(N6))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG6" s="7" t="e" cm="1">
-        <f t="array" ref="AG6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(O6,2-INT(LOG10(ABS(O6))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH6" s="7" t="e" cm="1">
-        <f t="array" ref="AH6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(P6,2-INT(LOG10(ABS(P6))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI6" s="7" t="e" cm="1">
-        <f t="array" ref="AI6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(Q6,2-INT(LOG10(ABS(Q6))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ6" s="7" t="e" cm="1">
-        <f t="array" ref="AJ6">SUMPRODUCT(--(ROUND($D6:$R6,2-INT(LOG10(ABS($D6:$R6))))&lt;ROUND(R6,2-INT(LOG10(ABS(R6))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V6" s="7" t="e">
+        <f>_xlfn.RANK.EQ(D6,$D6:$R6,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W6" s="7" t="e">
+        <f>_xlfn.RANK.EQ(E6,$D6:$R6,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X6" s="7" t="e">
+        <f>_xlfn.RANK.EQ(F6,$D6:$R6,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="Y6" s="7" t="e">
+        <f>_xlfn.RANK.EQ(G6,$D6:$R6,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="Z6" s="7" t="e">
+        <f>_xlfn.RANK.EQ(H6,$D6:$R6,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AA6" s="7" t="e">
+        <f>_xlfn.RANK.EQ(I6,$D6:$R6,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AB6" s="7" t="e">
+        <f>_xlfn.RANK.EQ(J6,$D6:$R6,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AC6" s="7" t="e">
+        <f>_xlfn.RANK.EQ(K6,$D6:$R6,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AD6" s="7" t="e">
+        <f>_xlfn.RANK.EQ(L6,$D6:$R6,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AE6" s="7" t="e">
+        <f>_xlfn.RANK.EQ(M6,$D6:$R6,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF6" s="7" t="e">
+        <f>_xlfn.RANK.EQ(N6,$D6:$R6,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AG6" s="7" t="e">
+        <f>_xlfn.RANK.EQ(O6,$D6:$R6,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AH6" s="7" t="e">
+        <f>_xlfn.RANK.EQ(P6,$D6:$R6,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AI6" s="7" t="e">
+        <f>_xlfn.RANK.EQ(Q6,$D6:$R6,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ6" s="7" t="e">
+        <f>_xlfn.RANK.EQ(R6,$D6:$R6,1)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A7" s="19"/>
+      <c r="A7" s="18"/>
       <c r="B7" s="10" t="s">
         <v>46</v>
       </c>
@@ -1742,7 +1637,7 @@
       <c r="AF7" s="7"/>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A8" s="19"/>
+      <c r="A8" s="18"/>
       <c r="B8" s="5" t="s">
         <v>46</v>
       </c>
@@ -1781,7 +1676,7 @@
       <c r="AF8" s="7"/>
     </row>
     <row r="9" spans="1:36" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="19"/>
+      <c r="A9" s="18"/>
       <c r="B9" s="2" t="s">
         <v>47</v>
       </c>
@@ -1809,69 +1704,69 @@
       <c r="T9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="V9" s="7" t="e" cm="1">
-        <f t="array" ref="V9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(D9,2-INT(LOG10(ABS(D9))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W9" s="7" t="e" cm="1">
-        <f t="array" ref="W9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(E9,2-INT(LOG10(ABS(E9))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X9" s="7" t="e" cm="1">
-        <f t="array" ref="X9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(F9,2-INT(LOG10(ABS(F9))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y9" s="7" t="e" cm="1">
-        <f t="array" ref="Y9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(G9,2-INT(LOG10(ABS(G9))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z9" s="7" t="e" cm="1">
-        <f t="array" ref="Z9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(H9,2-INT(LOG10(ABS(H9))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA9" s="7" t="e" cm="1">
-        <f t="array" ref="AA9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(I9,2-INT(LOG10(ABS(I9))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB9" s="7" t="e" cm="1">
-        <f t="array" ref="AB9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(J9,2-INT(LOG10(ABS(J9))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC9" s="7" t="e" cm="1">
-        <f t="array" ref="AC9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(K9,2-INT(LOG10(ABS(K9))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD9" s="7" t="e" cm="1">
-        <f t="array" ref="AD9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(L9,2-INT(LOG10(ABS(L9))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE9" s="7" t="e" cm="1">
-        <f t="array" ref="AE9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(M9,2-INT(LOG10(ABS(M9))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF9" s="7" t="e" cm="1">
-        <f t="array" ref="AF9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(N9,2-INT(LOG10(ABS(N9))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG9" s="7" t="e" cm="1">
-        <f t="array" ref="AG9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(O9,2-INT(LOG10(ABS(O9))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH9" s="7" t="e" cm="1">
-        <f t="array" ref="AH9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(P9,2-INT(LOG10(ABS(P9))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI9" s="7" t="e" cm="1">
-        <f t="array" ref="AI9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(Q9,2-INT(LOG10(ABS(Q9))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ9" s="7" t="e" cm="1">
-        <f t="array" ref="AJ9">SUMPRODUCT(--(ROUND($D9:$R9,2-INT(LOG10(ABS($D9:$R9))))&lt;ROUND(R9,2-INT(LOG10(ABS(R9))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V9" s="7" t="e">
+        <f>_xlfn.RANK.EQ(D9,$D9:$R9,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W9" s="7" t="e">
+        <f>_xlfn.RANK.EQ(E9,$D9:$R9,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X9" s="7" t="e">
+        <f>_xlfn.RANK.EQ(F9,$D9:$R9,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="Y9" s="7" t="e">
+        <f>_xlfn.RANK.EQ(G9,$D9:$R9,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="Z9" s="7" t="e">
+        <f>_xlfn.RANK.EQ(H9,$D9:$R9,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AA9" s="7" t="e">
+        <f>_xlfn.RANK.EQ(I9,$D9:$R9,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AB9" s="7" t="e">
+        <f>_xlfn.RANK.EQ(J9,$D9:$R9,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AC9" s="7" t="e">
+        <f>_xlfn.RANK.EQ(K9,$D9:$R9,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AD9" s="7" t="e">
+        <f>_xlfn.RANK.EQ(L9,$D9:$R9,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AE9" s="7" t="e">
+        <f>_xlfn.RANK.EQ(M9,$D9:$R9,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF9" s="7" t="e">
+        <f>_xlfn.RANK.EQ(N9,$D9:$R9,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AG9" s="7" t="e">
+        <f>_xlfn.RANK.EQ(O9,$D9:$R9,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AH9" s="7" t="e">
+        <f>_xlfn.RANK.EQ(P9,$D9:$R9,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AI9" s="7" t="e">
+        <f>_xlfn.RANK.EQ(Q9,$D9:$R9,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ9" s="7" t="e">
+        <f>_xlfn.RANK.EQ(R9,$D9:$R9,1)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A10" s="19"/>
+      <c r="A10" s="18"/>
       <c r="B10" s="10" t="s">
         <v>47</v>
       </c>
@@ -1910,7 +1805,7 @@
       <c r="AF10" s="7"/>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A11" s="19"/>
+      <c r="A11" s="18"/>
       <c r="B11" s="5" t="s">
         <v>47</v>
       </c>
@@ -1949,7 +1844,7 @@
       <c r="AF11" s="7"/>
     </row>
     <row r="12" spans="1:36" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="19"/>
+      <c r="A12" s="18"/>
       <c r="B12" s="2" t="s">
         <v>48</v>
       </c>
@@ -1977,69 +1872,69 @@
       <c r="T12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="V12" s="7" t="e" cm="1">
-        <f t="array" ref="V12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(D12,2-INT(LOG10(ABS(D12))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W12" s="7" t="e" cm="1">
-        <f t="array" ref="W12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(E12,2-INT(LOG10(ABS(E12))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X12" s="7" t="e" cm="1">
-        <f t="array" ref="X12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(F12,2-INT(LOG10(ABS(F12))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y12" s="7" t="e" cm="1">
-        <f t="array" ref="Y12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(G12,2-INT(LOG10(ABS(G12))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z12" s="7" t="e" cm="1">
-        <f t="array" ref="Z12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(H12,2-INT(LOG10(ABS(H12))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA12" s="7" t="e" cm="1">
-        <f t="array" ref="AA12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(I12,2-INT(LOG10(ABS(I12))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB12" s="7" t="e" cm="1">
-        <f t="array" ref="AB12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(J12,2-INT(LOG10(ABS(J12))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC12" s="7" t="e" cm="1">
-        <f t="array" ref="AC12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(K12,2-INT(LOG10(ABS(K12))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD12" s="7" t="e" cm="1">
-        <f t="array" ref="AD12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(L12,2-INT(LOG10(ABS(L12))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE12" s="7" t="e" cm="1">
-        <f t="array" ref="AE12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(M12,2-INT(LOG10(ABS(M12))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF12" s="7" t="e" cm="1">
-        <f t="array" ref="AF12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(N12,2-INT(LOG10(ABS(N12))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG12" s="7" t="e" cm="1">
-        <f t="array" ref="AG12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(O12,2-INT(LOG10(ABS(O12))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH12" s="7" t="e" cm="1">
-        <f t="array" ref="AH12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(P12,2-INT(LOG10(ABS(P12))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI12" s="7" t="e" cm="1">
-        <f t="array" ref="AI12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(Q12,2-INT(LOG10(ABS(Q12))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ12" s="7" t="e" cm="1">
-        <f t="array" ref="AJ12">SUMPRODUCT(--(ROUND($D12:$R12,2-INT(LOG10(ABS($D12:$R12))))&lt;ROUND(R12,2-INT(LOG10(ABS(R12))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V12" s="7" t="e">
+        <f>_xlfn.RANK.EQ(D12,$D12:$R12,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W12" s="7" t="e">
+        <f>_xlfn.RANK.EQ(E12,$D12:$R12,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X12" s="7" t="e">
+        <f>_xlfn.RANK.EQ(F12,$D12:$R12,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="Y12" s="7" t="e">
+        <f>_xlfn.RANK.EQ(G12,$D12:$R12,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="Z12" s="7" t="e">
+        <f>_xlfn.RANK.EQ(H12,$D12:$R12,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AA12" s="7" t="e">
+        <f>_xlfn.RANK.EQ(I12,$D12:$R12,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AB12" s="7" t="e">
+        <f>_xlfn.RANK.EQ(J12,$D12:$R12,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AC12" s="7" t="e">
+        <f>_xlfn.RANK.EQ(K12,$D12:$R12,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AD12" s="7" t="e">
+        <f>_xlfn.RANK.EQ(L12,$D12:$R12,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AE12" s="7" t="e">
+        <f>_xlfn.RANK.EQ(M12,$D12:$R12,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF12" s="7" t="e">
+        <f>_xlfn.RANK.EQ(N12,$D12:$R12,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AG12" s="7" t="e">
+        <f>_xlfn.RANK.EQ(O12,$D12:$R12,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AH12" s="7" t="e">
+        <f>_xlfn.RANK.EQ(P12,$D12:$R12,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AI12" s="7" t="e">
+        <f>_xlfn.RANK.EQ(Q12,$D12:$R12,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ12" s="7" t="e">
+        <f>_xlfn.RANK.EQ(R12,$D12:$R12,1)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A13" s="19"/>
+      <c r="A13" s="18"/>
       <c r="B13" s="10" t="s">
         <v>48</v>
       </c>
@@ -2078,7 +1973,7 @@
       <c r="AF13" s="7"/>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A14" s="23"/>
+      <c r="A14" s="22"/>
       <c r="B14" s="5" t="s">
         <v>48</v>
       </c>
@@ -2117,7 +2012,7 @@
       <c r="AF14" s="7"/>
     </row>
     <row r="15" spans="1:36" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="18" t="s">
         <v>17</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -2147,69 +2042,69 @@
       <c r="T15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="V15" s="7" t="e" cm="1">
-        <f t="array" ref="V15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(D15,2-INT(LOG10(ABS(D15))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W15" s="7" t="e" cm="1">
-        <f t="array" ref="W15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(E15,2-INT(LOG10(ABS(E15))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X15" s="7" t="e" cm="1">
-        <f t="array" ref="X15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(F15,2-INT(LOG10(ABS(F15))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y15" s="7" t="e" cm="1">
-        <f t="array" ref="Y15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(G15,2-INT(LOG10(ABS(G15))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z15" s="7" t="e" cm="1">
-        <f t="array" ref="Z15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(H15,2-INT(LOG10(ABS(H15))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA15" s="7" t="e" cm="1">
-        <f t="array" ref="AA15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(I15,2-INT(LOG10(ABS(I15))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB15" s="7" t="e" cm="1">
-        <f t="array" ref="AB15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(J15,2-INT(LOG10(ABS(J15))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC15" s="7" t="e" cm="1">
-        <f t="array" ref="AC15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(K15,2-INT(LOG10(ABS(K15))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD15" s="7" t="e" cm="1">
-        <f t="array" ref="AD15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(L15,2-INT(LOG10(ABS(L15))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE15" s="7" t="e" cm="1">
-        <f t="array" ref="AE15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(M15,2-INT(LOG10(ABS(M15))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF15" s="7" t="e" cm="1">
-        <f t="array" ref="AF15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(N15,2-INT(LOG10(ABS(N15))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG15" s="7" t="e" cm="1">
-        <f t="array" ref="AG15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(O15,2-INT(LOG10(ABS(O15))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH15" s="7" t="e" cm="1">
-        <f t="array" ref="AH15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(P15,2-INT(LOG10(ABS(P15))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI15" s="7" t="e" cm="1">
-        <f t="array" ref="AI15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(Q15,2-INT(LOG10(ABS(Q15))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ15" s="7" t="e" cm="1">
-        <f t="array" ref="AJ15">SUMPRODUCT(--(ROUND($D15:$R15,2-INT(LOG10(ABS($D15:$R15))))&lt;ROUND(R15,2-INT(LOG10(ABS(R15))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V15" s="7" t="e">
+        <f>_xlfn.RANK.EQ(D15,$D15:$R15,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W15" s="7" t="e">
+        <f>_xlfn.RANK.EQ(E15,$D15:$R15,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X15" s="7" t="e">
+        <f>_xlfn.RANK.EQ(F15,$D15:$R15,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="Y15" s="7" t="e">
+        <f>_xlfn.RANK.EQ(G15,$D15:$R15,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="Z15" s="7" t="e">
+        <f>_xlfn.RANK.EQ(H15,$D15:$R15,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AA15" s="7" t="e">
+        <f>_xlfn.RANK.EQ(I15,$D15:$R15,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AB15" s="7" t="e">
+        <f>_xlfn.RANK.EQ(J15,$D15:$R15,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AC15" s="7" t="e">
+        <f>_xlfn.RANK.EQ(K15,$D15:$R15,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AD15" s="7" t="e">
+        <f>_xlfn.RANK.EQ(L15,$D15:$R15,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AE15" s="7" t="e">
+        <f>_xlfn.RANK.EQ(M15,$D15:$R15,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF15" s="7" t="e">
+        <f>_xlfn.RANK.EQ(N15,$D15:$R15,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AG15" s="7" t="e">
+        <f>_xlfn.RANK.EQ(O15,$D15:$R15,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AH15" s="7" t="e">
+        <f>_xlfn.RANK.EQ(P15,$D15:$R15,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AI15" s="7" t="e">
+        <f>_xlfn.RANK.EQ(Q15,$D15:$R15,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ15" s="7" t="e">
+        <f>_xlfn.RANK.EQ(R15,$D15:$R15,1)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A16" s="19"/>
+      <c r="A16" s="18"/>
       <c r="B16" s="10" t="s">
         <v>49</v>
       </c>
@@ -2248,7 +2143,7 @@
       <c r="AF16" s="7"/>
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A17" s="19"/>
+      <c r="A17" s="18"/>
       <c r="B17" s="5" t="s">
         <v>49</v>
       </c>
@@ -2287,7 +2182,7 @@
       <c r="AF17" s="7"/>
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A18" s="19"/>
+      <c r="A18" s="18"/>
       <c r="B18" s="2" t="s">
         <v>50</v>
       </c>
@@ -2315,69 +2210,69 @@
       <c r="T18" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="V18" s="7" t="e" cm="1">
-        <f t="array" ref="V18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(D18,2-INT(LOG10(ABS(D18))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W18" s="7" t="e" cm="1">
-        <f t="array" ref="W18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(E18,2-INT(LOG10(ABS(E18))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X18" s="7" t="e" cm="1">
-        <f t="array" ref="X18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(F18,2-INT(LOG10(ABS(F18))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y18" s="7" t="e" cm="1">
-        <f t="array" ref="Y18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(G18,2-INT(LOG10(ABS(G18))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z18" s="7" t="e" cm="1">
-        <f t="array" ref="Z18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(H18,2-INT(LOG10(ABS(H18))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA18" s="7" t="e" cm="1">
-        <f t="array" ref="AA18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(I18,2-INT(LOG10(ABS(I18))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB18" s="7" t="e" cm="1">
-        <f t="array" ref="AB18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(J18,2-INT(LOG10(ABS(J18))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC18" s="7" t="e" cm="1">
-        <f t="array" ref="AC18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(K18,2-INT(LOG10(ABS(K18))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD18" s="7" t="e" cm="1">
-        <f t="array" ref="AD18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(L18,2-INT(LOG10(ABS(L18))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE18" s="7" t="e" cm="1">
-        <f t="array" ref="AE18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(M18,2-INT(LOG10(ABS(M18))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF18" s="7" t="e" cm="1">
-        <f t="array" ref="AF18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(N18,2-INT(LOG10(ABS(N18))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG18" s="7" t="e" cm="1">
-        <f t="array" ref="AG18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(O18,2-INT(LOG10(ABS(O18))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH18" s="7" t="e" cm="1">
-        <f t="array" ref="AH18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(P18,2-INT(LOG10(ABS(P18))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI18" s="7" t="e" cm="1">
-        <f t="array" ref="AI18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(Q18,2-INT(LOG10(ABS(Q18))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ18" s="7" t="e" cm="1">
-        <f t="array" ref="AJ18">SUMPRODUCT(--(ROUND($D18:$R18,2-INT(LOG10(ABS($D18:$R18))))&lt;ROUND(R18,2-INT(LOG10(ABS(R18))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V18" s="7" t="e">
+        <f>_xlfn.RANK.EQ(D18,$D18:$R18,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W18" s="7" t="e">
+        <f>_xlfn.RANK.EQ(E18,$D18:$R18,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X18" s="7" t="e">
+        <f>_xlfn.RANK.EQ(F18,$D18:$R18,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="Y18" s="7" t="e">
+        <f>_xlfn.RANK.EQ(G18,$D18:$R18,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="Z18" s="7" t="e">
+        <f>_xlfn.RANK.EQ(H18,$D18:$R18,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AA18" s="7" t="e">
+        <f>_xlfn.RANK.EQ(I18,$D18:$R18,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AB18" s="7" t="e">
+        <f>_xlfn.RANK.EQ(J18,$D18:$R18,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AC18" s="7" t="e">
+        <f>_xlfn.RANK.EQ(K18,$D18:$R18,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AD18" s="7" t="e">
+        <f>_xlfn.RANK.EQ(L18,$D18:$R18,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AE18" s="7" t="e">
+        <f>_xlfn.RANK.EQ(M18,$D18:$R18,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF18" s="7" t="e">
+        <f>_xlfn.RANK.EQ(N18,$D18:$R18,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AG18" s="7" t="e">
+        <f>_xlfn.RANK.EQ(O18,$D18:$R18,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AH18" s="7" t="e">
+        <f>_xlfn.RANK.EQ(P18,$D18:$R18,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AI18" s="7" t="e">
+        <f>_xlfn.RANK.EQ(Q18,$D18:$R18,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ18" s="7" t="e">
+        <f>_xlfn.RANK.EQ(R18,$D18:$R18,1)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="19" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A19" s="19"/>
+      <c r="A19" s="18"/>
       <c r="B19" s="10" t="s">
         <v>50</v>
       </c>
@@ -2416,7 +2311,7 @@
       <c r="AF19" s="7"/>
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A20" s="19"/>
+      <c r="A20" s="18"/>
       <c r="B20" s="5" t="s">
         <v>50</v>
       </c>
@@ -2455,7 +2350,7 @@
       <c r="AF20" s="7"/>
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A21" s="19"/>
+      <c r="A21" s="18"/>
       <c r="B21" s="2" t="s">
         <v>51</v>
       </c>
@@ -2483,69 +2378,69 @@
       <c r="T21" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="V21" s="7" t="e" cm="1">
-        <f t="array" ref="V21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(D21,2-INT(LOG10(ABS(D21))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W21" s="7" t="e" cm="1">
-        <f t="array" ref="W21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(E21,2-INT(LOG10(ABS(E21))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X21" s="7" t="e" cm="1">
-        <f t="array" ref="X21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(F21,2-INT(LOG10(ABS(F21))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y21" s="7" t="e" cm="1">
-        <f t="array" ref="Y21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(G21,2-INT(LOG10(ABS(G21))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z21" s="7" t="e" cm="1">
-        <f t="array" ref="Z21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(H21,2-INT(LOG10(ABS(H21))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA21" s="7" t="e" cm="1">
-        <f t="array" ref="AA21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(I21,2-INT(LOG10(ABS(I21))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB21" s="7" t="e" cm="1">
-        <f t="array" ref="AB21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(J21,2-INT(LOG10(ABS(J21))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC21" s="7" t="e" cm="1">
-        <f t="array" ref="AC21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(K21,2-INT(LOG10(ABS(K21))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD21" s="7" t="e" cm="1">
-        <f t="array" ref="AD21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(L21,2-INT(LOG10(ABS(L21))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE21" s="7" t="e" cm="1">
-        <f t="array" ref="AE21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(M21,2-INT(LOG10(ABS(M21))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF21" s="7" t="e" cm="1">
-        <f t="array" ref="AF21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(N21,2-INT(LOG10(ABS(N21))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG21" s="7" t="e" cm="1">
-        <f t="array" ref="AG21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(O21,2-INT(LOG10(ABS(O21))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH21" s="7" t="e" cm="1">
-        <f t="array" ref="AH21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(P21,2-INT(LOG10(ABS(P21))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI21" s="7" t="e" cm="1">
-        <f t="array" ref="AI21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(Q21,2-INT(LOG10(ABS(Q21))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ21" s="7" t="e" cm="1">
-        <f t="array" ref="AJ21">SUMPRODUCT(--(ROUND($D21:$R21,2-INT(LOG10(ABS($D21:$R21))))&lt;ROUND(R21,2-INT(LOG10(ABS(R21))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V21" s="7" t="e">
+        <f>_xlfn.RANK.EQ(D21,$D21:$R21,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W21" s="7" t="e">
+        <f>_xlfn.RANK.EQ(E21,$D21:$R21,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X21" s="7" t="e">
+        <f>_xlfn.RANK.EQ(F21,$D21:$R21,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="Y21" s="7" t="e">
+        <f>_xlfn.RANK.EQ(G21,$D21:$R21,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="Z21" s="7" t="e">
+        <f>_xlfn.RANK.EQ(H21,$D21:$R21,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AA21" s="7" t="e">
+        <f>_xlfn.RANK.EQ(I21,$D21:$R21,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AB21" s="7" t="e">
+        <f>_xlfn.RANK.EQ(J21,$D21:$R21,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AC21" s="7" t="e">
+        <f>_xlfn.RANK.EQ(K21,$D21:$R21,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AD21" s="7" t="e">
+        <f>_xlfn.RANK.EQ(L21,$D21:$R21,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AE21" s="7" t="e">
+        <f>_xlfn.RANK.EQ(M21,$D21:$R21,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF21" s="7" t="e">
+        <f>_xlfn.RANK.EQ(N21,$D21:$R21,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AG21" s="7" t="e">
+        <f>_xlfn.RANK.EQ(O21,$D21:$R21,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AH21" s="7" t="e">
+        <f>_xlfn.RANK.EQ(P21,$D21:$R21,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AI21" s="7" t="e">
+        <f>_xlfn.RANK.EQ(Q21,$D21:$R21,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ21" s="7" t="e">
+        <f>_xlfn.RANK.EQ(R21,$D21:$R21,1)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A22" s="19"/>
+      <c r="A22" s="18"/>
       <c r="B22" s="10" t="s">
         <v>51</v>
       </c>
@@ -2584,7 +2479,7 @@
       <c r="AF22" s="7"/>
     </row>
     <row r="23" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A23" s="23"/>
+      <c r="A23" s="22"/>
       <c r="B23" s="5" t="s">
         <v>51</v>
       </c>
@@ -2623,7 +2518,7 @@
       <c r="AF23" s="7"/>
     </row>
     <row r="24" spans="1:36" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="19" t="s">
+      <c r="A24" s="18" t="s">
         <v>19</v>
       </c>
       <c r="B24" s="2" t="s">
@@ -2653,69 +2548,69 @@
       <c r="T24" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="V24" s="7" t="e" cm="1">
-        <f t="array" ref="V24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(D24,2-INT(LOG10(ABS(D24))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W24" s="7" t="e" cm="1">
-        <f t="array" ref="W24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(E24,2-INT(LOG10(ABS(E24))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X24" s="7" t="e" cm="1">
-        <f t="array" ref="X24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(F24,2-INT(LOG10(ABS(F24))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y24" s="7" t="e" cm="1">
-        <f t="array" ref="Y24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(G24,2-INT(LOG10(ABS(G24))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z24" s="7" t="e" cm="1">
-        <f t="array" ref="Z24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(H24,2-INT(LOG10(ABS(H24))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA24" s="7" t="e" cm="1">
-        <f t="array" ref="AA24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(I24,2-INT(LOG10(ABS(I24))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB24" s="7" t="e" cm="1">
-        <f t="array" ref="AB24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(J24,2-INT(LOG10(ABS(J24))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC24" s="7" t="e" cm="1">
-        <f t="array" ref="AC24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(K24,2-INT(LOG10(ABS(K24))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD24" s="7" t="e" cm="1">
-        <f t="array" ref="AD24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(L24,2-INT(LOG10(ABS(L24))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE24" s="7" t="e" cm="1">
-        <f t="array" ref="AE24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(M24,2-INT(LOG10(ABS(M24))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF24" s="7" t="e" cm="1">
-        <f t="array" ref="AF24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(N24,2-INT(LOG10(ABS(N24))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG24" s="7" t="e" cm="1">
-        <f t="array" ref="AG24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(O24,2-INT(LOG10(ABS(O24))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH24" s="7" t="e" cm="1">
-        <f t="array" ref="AH24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(P24,2-INT(LOG10(ABS(P24))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI24" s="7" t="e" cm="1">
-        <f t="array" ref="AI24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(Q24,2-INT(LOG10(ABS(Q24))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ24" s="7" t="e" cm="1">
-        <f t="array" ref="AJ24">SUMPRODUCT(--(ROUND($D24:$R24,2-INT(LOG10(ABS($D24:$R24))))&lt;ROUND(R24,2-INT(LOG10(ABS(R24))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V24" s="7" t="e">
+        <f>_xlfn.RANK.EQ(D24,$D24:$R24,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W24" s="7" t="e">
+        <f>_xlfn.RANK.EQ(E24,$D24:$R24,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X24" s="7" t="e">
+        <f>_xlfn.RANK.EQ(F24,$D24:$R24,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="Y24" s="7" t="e">
+        <f>_xlfn.RANK.EQ(G24,$D24:$R24,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="Z24" s="7" t="e">
+        <f>_xlfn.RANK.EQ(H24,$D24:$R24,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AA24" s="7" t="e">
+        <f>_xlfn.RANK.EQ(I24,$D24:$R24,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AB24" s="7" t="e">
+        <f>_xlfn.RANK.EQ(J24,$D24:$R24,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AC24" s="7" t="e">
+        <f>_xlfn.RANK.EQ(K24,$D24:$R24,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AD24" s="7" t="e">
+        <f>_xlfn.RANK.EQ(L24,$D24:$R24,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AE24" s="7" t="e">
+        <f>_xlfn.RANK.EQ(M24,$D24:$R24,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF24" s="7" t="e">
+        <f>_xlfn.RANK.EQ(N24,$D24:$R24,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AG24" s="7" t="e">
+        <f>_xlfn.RANK.EQ(O24,$D24:$R24,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AH24" s="7" t="e">
+        <f>_xlfn.RANK.EQ(P24,$D24:$R24,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AI24" s="7" t="e">
+        <f>_xlfn.RANK.EQ(Q24,$D24:$R24,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ24" s="7" t="e">
+        <f>_xlfn.RANK.EQ(R24,$D24:$R24,1)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A25" s="19"/>
+      <c r="A25" s="18"/>
       <c r="B25" s="10" t="s">
         <v>52</v>
       </c>
@@ -2754,7 +2649,7 @@
       <c r="AF25" s="7"/>
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A26" s="19"/>
+      <c r="A26" s="18"/>
       <c r="B26" s="5" t="s">
         <v>52</v>
       </c>
@@ -2793,7 +2688,7 @@
       <c r="AF26" s="7"/>
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A27" s="19"/>
+      <c r="A27" s="18"/>
       <c r="B27" s="2" t="s">
         <v>53</v>
       </c>
@@ -2821,69 +2716,69 @@
       <c r="T27" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="V27" s="7" t="e" cm="1">
-        <f t="array" ref="V27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(D27,2-INT(LOG10(ABS(D27))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W27" s="7" t="e" cm="1">
-        <f t="array" ref="W27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(E27,2-INT(LOG10(ABS(E27))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X27" s="7" t="e" cm="1">
-        <f t="array" ref="X27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(F27,2-INT(LOG10(ABS(F27))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y27" s="7" t="e" cm="1">
-        <f t="array" ref="Y27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(G27,2-INT(LOG10(ABS(G27))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z27" s="7" t="e" cm="1">
-        <f t="array" ref="Z27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(H27,2-INT(LOG10(ABS(H27))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA27" s="7" t="e" cm="1">
-        <f t="array" ref="AA27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(I27,2-INT(LOG10(ABS(I27))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB27" s="7" t="e" cm="1">
-        <f t="array" ref="AB27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(J27,2-INT(LOG10(ABS(J27))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC27" s="7" t="e" cm="1">
-        <f t="array" ref="AC27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(K27,2-INT(LOG10(ABS(K27))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD27" s="7" t="e" cm="1">
-        <f t="array" ref="AD27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(L27,2-INT(LOG10(ABS(L27))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE27" s="7" t="e" cm="1">
-        <f t="array" ref="AE27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(M27,2-INT(LOG10(ABS(M27))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF27" s="7" t="e" cm="1">
-        <f t="array" ref="AF27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(N27,2-INT(LOG10(ABS(N27))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG27" s="7" t="e" cm="1">
-        <f t="array" ref="AG27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(O27,2-INT(LOG10(ABS(O27))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH27" s="7" t="e" cm="1">
-        <f t="array" ref="AH27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(P27,2-INT(LOG10(ABS(P27))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI27" s="7" t="e" cm="1">
-        <f t="array" ref="AI27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(Q27,2-INT(LOG10(ABS(Q27))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ27" s="7" t="e" cm="1">
-        <f t="array" ref="AJ27">SUMPRODUCT(--(ROUND($D27:$R27,2-INT(LOG10(ABS($D27:$R27))))&lt;ROUND(R27,2-INT(LOG10(ABS(R27))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V27" s="7" t="e">
+        <f>_xlfn.RANK.EQ(D27,$D27:$R27,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W27" s="7" t="e">
+        <f>_xlfn.RANK.EQ(E27,$D27:$R27,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X27" s="7" t="e">
+        <f>_xlfn.RANK.EQ(F27,$D27:$R27,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="Y27" s="7" t="e">
+        <f>_xlfn.RANK.EQ(G27,$D27:$R27,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="Z27" s="7" t="e">
+        <f>_xlfn.RANK.EQ(H27,$D27:$R27,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AA27" s="7" t="e">
+        <f>_xlfn.RANK.EQ(I27,$D27:$R27,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AB27" s="7" t="e">
+        <f>_xlfn.RANK.EQ(J27,$D27:$R27,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AC27" s="7" t="e">
+        <f>_xlfn.RANK.EQ(K27,$D27:$R27,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AD27" s="7" t="e">
+        <f>_xlfn.RANK.EQ(L27,$D27:$R27,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AE27" s="7" t="e">
+        <f>_xlfn.RANK.EQ(M27,$D27:$R27,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF27" s="7" t="e">
+        <f>_xlfn.RANK.EQ(N27,$D27:$R27,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AG27" s="7" t="e">
+        <f>_xlfn.RANK.EQ(O27,$D27:$R27,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AH27" s="7" t="e">
+        <f>_xlfn.RANK.EQ(P27,$D27:$R27,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AI27" s="7" t="e">
+        <f>_xlfn.RANK.EQ(Q27,$D27:$R27,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ27" s="7" t="e">
+        <f>_xlfn.RANK.EQ(R27,$D27:$R27,1)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="28" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A28" s="19"/>
+      <c r="A28" s="18"/>
       <c r="B28" s="10" t="s">
         <v>53</v>
       </c>
@@ -2922,7 +2817,7 @@
       <c r="AF28" s="7"/>
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A29" s="19"/>
+      <c r="A29" s="18"/>
       <c r="B29" s="5" t="s">
         <v>53</v>
       </c>
@@ -2961,7 +2856,7 @@
       <c r="AF29" s="7"/>
     </row>
     <row r="30" spans="1:36" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="19"/>
+      <c r="A30" s="18"/>
       <c r="B30" s="2" t="s">
         <v>54</v>
       </c>
@@ -2989,69 +2884,69 @@
       <c r="T30" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="V30" s="7" t="e" cm="1">
-        <f t="array" ref="V30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(D30,2-INT(LOG10(ABS(D30))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="W30" s="7" t="e" cm="1">
-        <f t="array" ref="W30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(E30,2-INT(LOG10(ABS(E30))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="X30" s="7" t="e" cm="1">
-        <f t="array" ref="X30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(F30,2-INT(LOG10(ABS(F30))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Y30" s="7" t="e" cm="1">
-        <f t="array" ref="Y30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(G30,2-INT(LOG10(ABS(G30))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Z30" s="7" t="e" cm="1">
-        <f t="array" ref="Z30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(H30,2-INT(LOG10(ABS(H30))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA30" s="7" t="e" cm="1">
-        <f t="array" ref="AA30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(I30,2-INT(LOG10(ABS(I30))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB30" s="7" t="e" cm="1">
-        <f t="array" ref="AB30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(J30,2-INT(LOG10(ABS(J30))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC30" s="7" t="e" cm="1">
-        <f t="array" ref="AC30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(K30,2-INT(LOG10(ABS(K30))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD30" s="7" t="e" cm="1">
-        <f t="array" ref="AD30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(L30,2-INT(LOG10(ABS(L30))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AE30" s="7" t="e" cm="1">
-        <f t="array" ref="AE30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(M30,2-INT(LOG10(ABS(M30))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AF30" s="7" t="e" cm="1">
-        <f t="array" ref="AF30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(N30,2-INT(LOG10(ABS(N30))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AG30" s="7" t="e" cm="1">
-        <f t="array" ref="AG30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(O30,2-INT(LOG10(ABS(O30))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH30" s="7" t="e" cm="1">
-        <f t="array" ref="AH30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(P30,2-INT(LOG10(ABS(P30))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI30" s="7" t="e" cm="1">
-        <f t="array" ref="AI30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(Q30,2-INT(LOG10(ABS(Q30))))))+1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AJ30" s="7" t="e" cm="1">
-        <f t="array" ref="AJ30">SUMPRODUCT(--(ROUND($D30:$R30,2-INT(LOG10(ABS($D30:$R30))))&lt;ROUND(R30,2-INT(LOG10(ABS(R30))))))+1</f>
-        <v>#NUM!</v>
+      <c r="V30" s="7" t="e">
+        <f>_xlfn.RANK.EQ(D30,$D30:$R30,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W30" s="7" t="e">
+        <f>_xlfn.RANK.EQ(E30,$D30:$R30,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X30" s="7" t="e">
+        <f>_xlfn.RANK.EQ(F30,$D30:$R30,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="Y30" s="7" t="e">
+        <f>_xlfn.RANK.EQ(G30,$D30:$R30,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="Z30" s="7" t="e">
+        <f>_xlfn.RANK.EQ(H30,$D30:$R30,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AA30" s="7" t="e">
+        <f>_xlfn.RANK.EQ(I30,$D30:$R30,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AB30" s="7" t="e">
+        <f>_xlfn.RANK.EQ(J30,$D30:$R30,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AC30" s="7" t="e">
+        <f>_xlfn.RANK.EQ(K30,$D30:$R30,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AD30" s="7" t="e">
+        <f>_xlfn.RANK.EQ(L30,$D30:$R30,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AE30" s="7" t="e">
+        <f>_xlfn.RANK.EQ(M30,$D30:$R30,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF30" s="7" t="e">
+        <f>_xlfn.RANK.EQ(N30,$D30:$R30,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AG30" s="7" t="e">
+        <f>_xlfn.RANK.EQ(O30,$D30:$R30,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AH30" s="7" t="e">
+        <f>_xlfn.RANK.EQ(P30,$D30:$R30,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AI30" s="7" t="e">
+        <f>_xlfn.RANK.EQ(Q30,$D30:$R30,1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ30" s="7" t="e">
+        <f>_xlfn.RANK.EQ(R30,$D30:$R30,1)</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A31" s="19"/>
+      <c r="A31" s="18"/>
       <c r="B31" s="10" t="s">
         <v>54</v>
       </c>
@@ -3090,7 +2985,7 @@
       <c r="AF31" s="7"/>
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A32" s="23"/>
+      <c r="A32" s="22"/>
       <c r="B32" s="5" t="s">
         <v>54</v>
       </c>
@@ -3129,11 +3024,11 @@
       <c r="AF32" s="7"/>
     </row>
     <row r="33" spans="1:32" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="25" t="s">
+      <c r="A33" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="26"/>
-      <c r="C33" s="26"/>
+      <c r="B33" s="25"/>
+      <c r="C33" s="25"/>
       <c r="D33" s="7">
         <f>COUNTIF(V3:V32,1)</f>
         <v>0</v>
@@ -3207,11 +3102,11 @@
       <c r="AF33" s="7"/>
     </row>
     <row r="34" spans="1:32" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="19" t="s">
+      <c r="A34" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B34" s="20"/>
-      <c r="C34" s="20"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
       <c r="D34" s="7">
         <f>_xlfn.RANK.EQ(D33,$D33:$R33,0)</f>
         <v>1</v>
@@ -3285,70 +3180,70 @@
       <c r="AF34" s="7"/>
     </row>
     <row r="35" spans="1:32" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="22" t="s">
+      <c r="A35" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="B35" s="20"/>
-      <c r="C35" s="20"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
       <c r="D35" s="8" t="e">
         <f>AVERAGE(V3:V32)</f>
-        <v>#NUM!</v>
+        <v>#N/A</v>
       </c>
       <c r="E35" s="8" t="e">
         <f t="shared" ref="E35:R35" si="3">AVERAGE(W3:W32)</f>
-        <v>#NUM!</v>
+        <v>#N/A</v>
       </c>
       <c r="F35" s="8" t="e">
         <f t="shared" si="3"/>
-        <v>#NUM!</v>
+        <v>#N/A</v>
       </c>
       <c r="G35" s="8" t="e">
         <f t="shared" si="3"/>
-        <v>#NUM!</v>
+        <v>#N/A</v>
       </c>
       <c r="H35" s="8" t="e">
         <f t="shared" si="3"/>
-        <v>#NUM!</v>
+        <v>#N/A</v>
       </c>
       <c r="I35" s="8" t="e">
         <f t="shared" si="3"/>
-        <v>#NUM!</v>
+        <v>#N/A</v>
       </c>
       <c r="J35" s="8" t="e">
         <f t="shared" si="3"/>
-        <v>#NUM!</v>
+        <v>#N/A</v>
       </c>
       <c r="K35" s="8" t="e">
         <f t="shared" si="3"/>
-        <v>#NUM!</v>
+        <v>#N/A</v>
       </c>
       <c r="L35" s="8" t="e">
         <f t="shared" si="3"/>
-        <v>#NUM!</v>
+        <v>#N/A</v>
       </c>
       <c r="M35" s="8" t="e">
         <f t="shared" si="3"/>
-        <v>#NUM!</v>
+        <v>#N/A</v>
       </c>
       <c r="N35" s="8" t="e">
         <f t="shared" si="3"/>
-        <v>#NUM!</v>
+        <v>#N/A</v>
       </c>
       <c r="O35" s="8" t="e">
         <f t="shared" si="3"/>
-        <v>#NUM!</v>
+        <v>#N/A</v>
       </c>
       <c r="P35" s="8" t="e">
         <f t="shared" si="3"/>
-        <v>#NUM!</v>
+        <v>#N/A</v>
       </c>
       <c r="Q35" s="8" t="e">
         <f t="shared" si="3"/>
-        <v>#NUM!</v>
+        <v>#N/A</v>
       </c>
       <c r="R35" s="8" t="e">
         <f t="shared" si="3"/>
-        <v>#NUM!</v>
+        <v>#N/A</v>
       </c>
       <c r="V35" s="7"/>
       <c r="W35" s="7"/>
@@ -3363,70 +3258,70 @@
       <c r="AF35" s="7"/>
     </row>
     <row r="36" spans="1:32" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="23" t="s">
+      <c r="A36" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="B36" s="24"/>
-      <c r="C36" s="24"/>
+      <c r="B36" s="23"/>
+      <c r="C36" s="23"/>
       <c r="D36" s="5" t="e">
         <f>_xlfn.RANK.EQ(D35,$D35:$R35,1)</f>
-        <v>#NUM!</v>
+        <v>#N/A</v>
       </c>
       <c r="E36" s="5" t="e">
         <f t="shared" ref="E36:R36" si="4">_xlfn.RANK.EQ(E35,$D35:$R35,1)</f>
-        <v>#NUM!</v>
+        <v>#N/A</v>
       </c>
       <c r="F36" s="5" t="e">
         <f t="shared" si="4"/>
-        <v>#NUM!</v>
+        <v>#N/A</v>
       </c>
       <c r="G36" s="5" t="e">
         <f t="shared" si="4"/>
-        <v>#NUM!</v>
+        <v>#N/A</v>
       </c>
       <c r="H36" s="5" t="e">
         <f t="shared" si="4"/>
-        <v>#NUM!</v>
+        <v>#N/A</v>
       </c>
       <c r="I36" s="5" t="e">
         <f t="shared" si="4"/>
-        <v>#NUM!</v>
+        <v>#N/A</v>
       </c>
       <c r="J36" s="5" t="e">
         <f t="shared" si="4"/>
-        <v>#NUM!</v>
+        <v>#N/A</v>
       </c>
       <c r="K36" s="5" t="e">
         <f t="shared" si="4"/>
-        <v>#NUM!</v>
+        <v>#N/A</v>
       </c>
       <c r="L36" s="5" t="e">
         <f t="shared" si="4"/>
-        <v>#NUM!</v>
+        <v>#N/A</v>
       </c>
       <c r="M36" s="5" t="e">
         <f t="shared" si="4"/>
-        <v>#NUM!</v>
+        <v>#N/A</v>
       </c>
       <c r="N36" s="5" t="e">
         <f t="shared" si="4"/>
-        <v>#NUM!</v>
+        <v>#N/A</v>
       </c>
       <c r="O36" s="5" t="e">
         <f t="shared" si="4"/>
-        <v>#NUM!</v>
+        <v>#N/A</v>
       </c>
       <c r="P36" s="5" t="e">
         <f t="shared" si="4"/>
-        <v>#NUM!</v>
+        <v>#N/A</v>
       </c>
       <c r="Q36" s="5" t="e">
         <f t="shared" si="4"/>
-        <v>#NUM!</v>
+        <v>#N/A</v>
       </c>
       <c r="R36" s="5" t="e">
         <f t="shared" si="4"/>
-        <v>#NUM!</v>
+        <v>#N/A</v>
       </c>
       <c r="V36" s="7"/>
       <c r="W36" s="7"/>
@@ -3532,54 +3427,34 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="D3:R3">
-    <cfRule type="expression" dxfId="9" priority="10">
-      <formula>ROUND(D3,2-INT(LOG10(ABS(D3))))= ROUND(MIN($D3:$R3),2-INT(LOG10(ABS(MIN($D3:$R3)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="13" priority="10" bottom="1" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6:R6">
-    <cfRule type="expression" dxfId="8" priority="9">
-      <formula>ROUND(D6,2-INT(LOG10(ABS(D6))))= ROUND(MIN($D6:$R6),2-INT(LOG10(ABS(MIN($D6:$R6)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="12" priority="9" bottom="1" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:R9">
-    <cfRule type="expression" dxfId="7" priority="8">
-      <formula>ROUND(D9,2-INT(LOG10(ABS(D9))))= ROUND(MIN($D9:$R9),2-INT(LOG10(ABS(MIN($D9:$R9)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="11" priority="8" bottom="1" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D12:R12">
-    <cfRule type="expression" dxfId="6" priority="7">
-      <formula>ROUND(D12,2-INT(LOG10(ABS(D12))))= ROUND(MIN($D12:$R12),2-INT(LOG10(ABS(MIN($D12:$R12)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="10" priority="7" bottom="1" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D15:R15">
-    <cfRule type="expression" dxfId="5" priority="6">
-      <formula>ROUND(D15,2-INT(LOG10(ABS(D15))))= ROUND(MIN($D15:$R15),2-INT(LOG10(ABS(MIN($D15:$R15)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="9" priority="6" bottom="1" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D18:R18">
-    <cfRule type="expression" dxfId="4" priority="5">
-      <formula>ROUND(D18,2-INT(LOG10(ABS(D18))))= ROUND(MIN($D18:$R18),2-INT(LOG10(ABS(MIN($D18:$R18)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="8" priority="5" bottom="1" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D21:R21">
-    <cfRule type="expression" dxfId="3" priority="4">
-      <formula>ROUND(D21,2-INT(LOG10(ABS(D21))))= ROUND(MIN($D21:$R21),2-INT(LOG10(ABS(MIN($D21:$R21)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="7" priority="4" bottom="1" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D24:R24">
-    <cfRule type="expression" dxfId="2" priority="3">
-      <formula>ROUND(D24,2-INT(LOG10(ABS(D24))))= ROUND(MIN($D24:$R24),2-INT(LOG10(ABS(MIN($D24:$R24)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="6" priority="3" bottom="1" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D27:R27">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>ROUND(D27,2-INT(LOG10(ABS(D27))))= ROUND(MIN($D27:$R27),2-INT(LOG10(ABS(MIN($D27:$R27)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="5" priority="2" bottom="1" rank="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D30:R30">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>ROUND(D30,2-INT(LOG10(ABS(D30))))= ROUND(MIN($D30:$R30),2-INT(LOG10(ABS(MIN($D30:$R30)))))</formula>
-    </cfRule>
+    <cfRule type="top10" dxfId="4" priority="1" bottom="1" rank="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -3599,68 +3474,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="27" t="s">
         <v>145</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="27" t="s">
         <v>146</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="27" t="s">
         <v>147</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="27" t="s">
         <v>148</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="27" t="s">
         <v>150</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="27" t="s">
         <v>151</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="27" t="s">
         <v>152</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="K2" s="18" t="s">
+      <c r="K2" s="27" t="s">
         <v>154</v>
       </c>
-      <c r="L2" s="18" t="s">
+      <c r="L2" s="27" t="s">
         <v>155</v>
       </c>
-      <c r="M2" s="18" t="s">
+      <c r="M2" s="27" t="s">
         <v>156</v>
       </c>
-      <c r="N2" s="18" t="s">
+      <c r="N2" s="27" t="s">
         <v>157</v>
       </c>
-      <c r="O2" s="18" t="s">
+      <c r="O2" s="27" t="s">
         <v>158</v>
       </c>
     </row>
@@ -3859,7 +3734,7 @@
     <mergeCell ref="A1:O1"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:O12">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3878,68 +3753,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="27" t="s">
         <v>145</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="27" t="s">
         <v>146</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="27" t="s">
         <v>147</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="27" t="s">
         <v>148</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="27" t="s">
         <v>150</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="27" t="s">
         <v>151</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="27" t="s">
         <v>152</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="K2" s="18" t="s">
+      <c r="K2" s="27" t="s">
         <v>154</v>
       </c>
-      <c r="L2" s="18" t="s">
+      <c r="L2" s="27" t="s">
         <v>155</v>
       </c>
-      <c r="M2" s="18" t="s">
+      <c r="M2" s="27" t="s">
         <v>156</v>
       </c>
-      <c r="N2" s="18" t="s">
+      <c r="N2" s="27" t="s">
         <v>157</v>
       </c>
-      <c r="O2" s="18" t="s">
+      <c r="O2" s="27" t="s">
         <v>158</v>
       </c>
     </row>
@@ -4138,7 +4013,7 @@
     <mergeCell ref="A1:O1"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:O12">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4157,68 +4032,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="27" t="s">
         <v>145</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="27" t="s">
         <v>146</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="27" t="s">
         <v>147</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="27" t="s">
         <v>148</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="27" t="s">
         <v>150</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="27" t="s">
         <v>151</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="27" t="s">
         <v>152</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="K2" s="18" t="s">
+      <c r="K2" s="27" t="s">
         <v>154</v>
       </c>
-      <c r="L2" s="18" t="s">
+      <c r="L2" s="27" t="s">
         <v>155</v>
       </c>
-      <c r="M2" s="18" t="s">
+      <c r="M2" s="27" t="s">
         <v>156</v>
       </c>
-      <c r="N2" s="18" t="s">
+      <c r="N2" s="27" t="s">
         <v>157</v>
       </c>
-      <c r="O2" s="18" t="s">
+      <c r="O2" s="27" t="s">
         <v>158</v>
       </c>
     </row>
@@ -4417,7 +4292,7 @@
     <mergeCell ref="A1:O1"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:O12">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4436,68 +4311,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="27" t="s">
         <v>145</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="27" t="s">
         <v>146</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="27" t="s">
         <v>147</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="27" t="s">
         <v>148</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="27" t="s">
         <v>150</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="27" t="s">
         <v>151</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="27" t="s">
         <v>152</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="K2" s="18" t="s">
+      <c r="K2" s="27" t="s">
         <v>154</v>
       </c>
-      <c r="L2" s="18" t="s">
+      <c r="L2" s="27" t="s">
         <v>155</v>
       </c>
-      <c r="M2" s="18" t="s">
+      <c r="M2" s="27" t="s">
         <v>156</v>
       </c>
-      <c r="N2" s="18" t="s">
+      <c r="N2" s="27" t="s">
         <v>157</v>
       </c>
-      <c r="O2" s="18" t="s">
+      <c r="O2" s="27" t="s">
         <v>158</v>
       </c>
     </row>
@@ -4696,7 +4571,7 @@
     <mergeCell ref="A1:O1"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:O12">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4716,68 +4591,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="27" t="s">
         <v>145</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="27" t="s">
         <v>146</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="27" t="s">
         <v>147</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="27" t="s">
         <v>148</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="27" t="s">
         <v>150</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="27" t="s">
         <v>151</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="27" t="s">
         <v>152</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="K2" s="18" t="s">
+      <c r="K2" s="27" t="s">
         <v>154</v>
       </c>
-      <c r="L2" s="18" t="s">
+      <c r="L2" s="27" t="s">
         <v>155</v>
       </c>
-      <c r="M2" s="18" t="s">
+      <c r="M2" s="27" t="s">
         <v>156</v>
       </c>
-      <c r="N2" s="18" t="s">
+      <c r="N2" s="27" t="s">
         <v>157</v>
       </c>
-      <c r="O2" s="18" t="s">
+      <c r="O2" s="27" t="s">
         <v>158</v>
       </c>
     </row>

--- a/src/results_template/CEC2020/10Dim.xlsx
+++ b/src/results_template/CEC2020/10Dim.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\Research\Project Test\Base-Optimization-Framework\src\results_template\CEC2020\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\Research\Project Test\src\results_template\CEC2020\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{37DB59CC-1976-4905-9320-A983A76694DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{984173A0-D9B6-43B0-82A5-B6195479372E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Conclusions" sheetId="1" r:id="rId1"/>
@@ -22,20 +22,8 @@
     <sheet name="Friedman" sheetId="7" r:id="rId7"/>
     <sheet name="Explanation" sheetId="8" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <calcPr calcId="0"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -44,12 +32,57 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="101">
   <si>
     <t>Comparison of optimization results for the CEC benchmark functions 2020 (10 Dim)</t>
   </si>
   <si>
     <t>Functions</t>
+  </si>
+  <si>
+    <t>Algorithm 1</t>
+  </si>
+  <si>
+    <t>Algorithm 2</t>
+  </si>
+  <si>
+    <t>Algorithm 3</t>
+  </si>
+  <si>
+    <t>Algorithm 4</t>
+  </si>
+  <si>
+    <t>Algorithm 5</t>
+  </si>
+  <si>
+    <t>Algorithm 6</t>
+  </si>
+  <si>
+    <t>Algorithm 7</t>
+  </si>
+  <si>
+    <t>Algorithm 8</t>
+  </si>
+  <si>
+    <t>Algorithm 9</t>
+  </si>
+  <si>
+    <t>Algorithm 10</t>
+  </si>
+  <si>
+    <t>Algorithm 11</t>
+  </si>
+  <si>
+    <t>Algorithm 12</t>
+  </si>
+  <si>
+    <t>Algorithm 13</t>
+  </si>
+  <si>
+    <t>Algorithm 14</t>
+  </si>
+  <si>
+    <t>Algorithm 15</t>
   </si>
   <si>
     <t>Unimodal
@@ -107,177 +140,129 @@
     <t>F10</t>
   </si>
   <si>
-    <t>Algorithm 1</t>
-  </si>
-  <si>
-    <t>Algorithm 2</t>
-  </si>
-  <si>
-    <t>Algorithm 3</t>
-  </si>
-  <si>
-    <t>Algorithm 4</t>
-  </si>
-  <si>
-    <t>Algorithm 5</t>
-  </si>
-  <si>
-    <t>Algorithm 6</t>
-  </si>
-  <si>
-    <t>Algorithm 7</t>
-  </si>
-  <si>
-    <t>Algorithm 8</t>
-  </si>
-  <si>
-    <t>Algorithm 9</t>
-  </si>
-  <si>
-    <t>Algorithm 10</t>
-  </si>
-  <si>
-    <t>Algorithm 11</t>
-  </si>
-  <si>
-    <t>Algorithm 12</t>
-  </si>
-  <si>
-    <t>Algorithm 13</t>
-  </si>
-  <si>
-    <t>Algorithm 14</t>
-  </si>
-  <si>
-    <t>Algorithm 15</t>
-  </si>
-  <si>
-    <t>Number of Best Functions</t>
+    <t>P-value of the one-sided Welch t-test for the CEC benchmark functions 2020 (10 Dim)</t>
+  </si>
+  <si>
+    <t>Function</t>
+  </si>
+  <si>
+    <t>alg_base vs alg2</t>
+  </si>
+  <si>
+    <t>alg_base vs alg3</t>
+  </si>
+  <si>
+    <t>alg_base vs alg4</t>
+  </si>
+  <si>
+    <t>alg_base vs alg5</t>
+  </si>
+  <si>
+    <t>alg_base vs alg6</t>
+  </si>
+  <si>
+    <t>alg_base vs alg7</t>
+  </si>
+  <si>
+    <t>alg_base vs alg8</t>
+  </si>
+  <si>
+    <t>alg_base vs alg9</t>
+  </si>
+  <si>
+    <t>alg_base vs alg10</t>
+  </si>
+  <si>
+    <t>alg_base vs alg11</t>
+  </si>
+  <si>
+    <t>alg_base vs alg12</t>
+  </si>
+  <si>
+    <t>alg_base vs alg13</t>
+  </si>
+  <si>
+    <t>alg_base vs alg14</t>
+  </si>
+  <si>
+    <t>alg_base vs alg15</t>
+  </si>
+  <si>
+    <t>Decision (h) of the one-sided Welch t-test for the CEC benchmark functions 2020 (10 Dim)</t>
+  </si>
+  <si>
+    <t>P-value of the one-sided Wilcoxon rank-sum test for the CEC benchmark functions 2020 (10 Dim)</t>
+  </si>
+  <si>
+    <t>Decision (h) of the one-sided Wilcoxon rank-sum test for the CEC benchmark functions 2020 (10 Dim)</t>
+  </si>
+  <si>
+    <t>Rank-sum statistic (W) for the Wilcoxon rank-sum test for the CEC benchmark functions 2020 (10 Dim)</t>
+  </si>
+  <si>
+    <t>Function ranking and overall Friedman analysis for the CEC benchmark functions 2020 (10 Dim)</t>
+  </si>
+  <si>
+    <t>Algorithm 1 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 2 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 3 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 4 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 5 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 6 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 7 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 8 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 9 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 10 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 11 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 12 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 13 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 14 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 15 Rank</t>
+  </si>
+  <si>
+    <t>Best Algorithm</t>
+  </si>
+  <si>
+    <t>Kruskal-Wallis p</t>
+  </si>
+  <si>
+    <t>Significant?</t>
+  </si>
+  <si>
+    <t>Average Rank</t>
   </si>
   <si>
     <t>Overall Rank</t>
   </si>
   <si>
-    <t>P-value of the one-sided Welch t-test for the CEC benchmark functions 2020 (10 Dim)</t>
-  </si>
-  <si>
-    <t>Function</t>
-  </si>
-  <si>
-    <t>alg_base vs alg2</t>
-  </si>
-  <si>
-    <t>alg_base vs alg3</t>
-  </si>
-  <si>
-    <t>alg_base vs alg4</t>
-  </si>
-  <si>
-    <t>alg_base vs alg5</t>
-  </si>
-  <si>
-    <t>alg_base vs alg6</t>
-  </si>
-  <si>
-    <t>alg_base vs alg7</t>
-  </si>
-  <si>
-    <t>alg_base vs alg8</t>
-  </si>
-  <si>
-    <t>alg_base vs alg9</t>
-  </si>
-  <si>
-    <t>alg_base vs alg10</t>
-  </si>
-  <si>
-    <t>alg_base vs alg11</t>
-  </si>
-  <si>
-    <t>alg_base vs alg12</t>
-  </si>
-  <si>
-    <t>alg_base vs alg13</t>
-  </si>
-  <si>
-    <t>alg_base vs alg14</t>
-  </si>
-  <si>
-    <t>alg_base vs alg15</t>
-  </si>
-  <si>
-    <t>Decision (h) of the one-sided Welch t-test for the CEC benchmark functions 2020 (10 Dim)</t>
-  </si>
-  <si>
-    <t>P-value of the one-sided Wilcoxon rank-sum test for the CEC benchmark functions 2020 (10 Dim)</t>
-  </si>
-  <si>
-    <t>Decision (h) of the one-sided Wilcoxon rank-sum test for the CEC benchmark functions 2020 (10 Dim)</t>
-  </si>
-  <si>
-    <t>Rank-sum statistic (W) for the Wilcoxon rank-sum test for the CEC benchmark functions 2020 (10 Dim)</t>
-  </si>
-  <si>
-    <t>Function ranking and overall Friedman analysis for the CEC benchmark functions 2020 (10 Dim)</t>
-  </si>
-  <si>
-    <t>Algorithm 1 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 2 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 3 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 4 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 5 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 6 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 7 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 8 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 9 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 10 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 11 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 12 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 13 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 14 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 15 Rank</t>
-  </si>
-  <si>
-    <t>Best Algorithm</t>
-  </si>
-  <si>
-    <t>Kruskal-Wallis p</t>
-  </si>
-  <si>
-    <t>Significant?</t>
-  </si>
-  <si>
-    <t>Average Rank</t>
-  </si>
-  <si>
     <t>Overall Friedman Test</t>
   </si>
   <si>
@@ -348,6 +333,12 @@
   </si>
   <si>
     <t>Optional figures showing the distribution of final objective values across independent runs for each function and algorithm.</t>
+  </si>
+  <si>
+    <t>Total number of best answers</t>
+  </si>
+  <si>
+    <t>Total number of equal-best answers</t>
   </si>
 </sst>
 </file>
@@ -484,7 +475,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -529,7 +520,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -545,23 +535,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="11" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -569,14 +544,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -723,9 +720,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -830,99 +827,99 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R34"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.109375" style="6" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" style="6" customWidth="1"/>
     <col min="2" max="2" width="4" style="6" customWidth="1"/>
     <col min="3" max="3" width="6" style="6" customWidth="1"/>
-    <col min="4" max="12" width="11.33203125" style="6" customWidth="1"/>
-    <col min="13" max="18" width="12.33203125" style="6" customWidth="1"/>
-    <col min="19" max="16384" width="8.88671875" style="6"/>
+    <col min="4" max="12" width="11.28515625" style="6" customWidth="1"/>
+    <col min="13" max="18" width="12.28515625" style="6" customWidth="1"/>
+    <col min="19" max="16384" width="8.85546875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="27" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
-      <c r="Q1" s="27"/>
-      <c r="R1" s="27"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="31"/>
+      <c r="Q1" s="31"/>
+      <c r="R1" s="31"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -940,13 +937,11 @@
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="26"/>
-      <c r="B4" s="8" t="s">
-        <v>3</v>
-      </c>
+    <row r="4" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="30"/>
+      <c r="B4" s="28"/>
       <c r="C4" s="8" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
@@ -964,13 +959,11 @@
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A5" s="28"/>
-      <c r="B5" s="4" t="s">
-        <v>3</v>
-      </c>
+    <row r="5" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="33"/>
+      <c r="B5" s="29"/>
       <c r="C5" s="4" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
@@ -988,15 +981,15 @@
       <c r="Q5" s="5"/>
       <c r="R5" s="5"/>
     </row>
-    <row r="6" spans="1:18" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>8</v>
+    <row r="6" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>23</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -1014,13 +1007,11 @@
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A7" s="26"/>
-      <c r="B7" s="8" t="s">
-        <v>8</v>
-      </c>
+    <row r="7" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="30"/>
+      <c r="B7" s="28"/>
       <c r="C7" s="8" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
@@ -1038,13 +1029,11 @@
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A8" s="26"/>
-      <c r="B8" s="4" t="s">
-        <v>8</v>
-      </c>
+    <row r="8" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="30"/>
+      <c r="B8" s="29"/>
       <c r="C8" s="4" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
@@ -1062,13 +1051,13 @@
       <c r="Q8" s="5"/>
       <c r="R8" s="5"/>
     </row>
-    <row r="9" spans="1:18" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="26"/>
-      <c r="B9" s="2" t="s">
-        <v>9</v>
+    <row r="9" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="30"/>
+      <c r="B9" s="27" t="s">
+        <v>24</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -1086,13 +1075,11 @@
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A10" s="26"/>
-      <c r="B10" s="8" t="s">
-        <v>9</v>
-      </c>
+    <row r="10" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="30"/>
+      <c r="B10" s="28"/>
       <c r="C10" s="8" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
@@ -1110,13 +1097,11 @@
       <c r="Q10" s="7"/>
       <c r="R10" s="7"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A11" s="26"/>
-      <c r="B11" s="4" t="s">
-        <v>9</v>
-      </c>
+    <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="30"/>
+      <c r="B11" s="29"/>
       <c r="C11" s="4" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
@@ -1134,13 +1119,13 @@
       <c r="Q11" s="5"/>
       <c r="R11" s="5"/>
     </row>
-    <row r="12" spans="1:18" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="26"/>
-      <c r="B12" s="2" t="s">
-        <v>10</v>
+    <row r="12" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="30"/>
+      <c r="B12" s="27" t="s">
+        <v>25</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -1158,13 +1143,11 @@
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A13" s="26"/>
-      <c r="B13" s="8" t="s">
-        <v>10</v>
-      </c>
+    <row r="13" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="30"/>
+      <c r="B13" s="28"/>
       <c r="C13" s="8" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
@@ -1182,13 +1165,11 @@
       <c r="Q13" s="7"/>
       <c r="R13" s="7"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A14" s="28"/>
-      <c r="B14" s="4" t="s">
-        <v>10</v>
-      </c>
+    <row r="14" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="33"/>
+      <c r="B14" s="29"/>
       <c r="C14" s="4" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
@@ -1206,15 +1187,15 @@
       <c r="Q14" s="5"/>
       <c r="R14" s="5"/>
     </row>
-    <row r="15" spans="1:18" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>12</v>
+    <row r="15" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="27" t="s">
+        <v>27</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -1232,13 +1213,11 @@
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A16" s="26"/>
-      <c r="B16" s="8" t="s">
-        <v>12</v>
-      </c>
+    <row r="16" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="30"/>
+      <c r="B16" s="28"/>
       <c r="C16" s="8" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
@@ -1256,13 +1235,11 @@
       <c r="Q16" s="7"/>
       <c r="R16" s="7"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A17" s="26"/>
-      <c r="B17" s="4" t="s">
-        <v>12</v>
-      </c>
+    <row r="17" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="30"/>
+      <c r="B17" s="29"/>
       <c r="C17" s="4" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
@@ -1280,13 +1257,13 @@
       <c r="Q17" s="5"/>
       <c r="R17" s="5"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A18" s="26"/>
-      <c r="B18" s="2" t="s">
-        <v>13</v>
+    <row r="18" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="30"/>
+      <c r="B18" s="27" t="s">
+        <v>28</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -1304,13 +1281,11 @@
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A19" s="26"/>
-      <c r="B19" s="8" t="s">
-        <v>13</v>
-      </c>
+    <row r="19" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="30"/>
+      <c r="B19" s="28"/>
       <c r="C19" s="8" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
@@ -1328,13 +1303,11 @@
       <c r="Q19" s="7"/>
       <c r="R19" s="7"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A20" s="26"/>
-      <c r="B20" s="4" t="s">
-        <v>13</v>
-      </c>
+    <row r="20" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="30"/>
+      <c r="B20" s="29"/>
       <c r="C20" s="4" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
@@ -1352,13 +1325,13 @@
       <c r="Q20" s="5"/>
       <c r="R20" s="5"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A21" s="26"/>
-      <c r="B21" s="2" t="s">
-        <v>14</v>
+    <row r="21" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="30"/>
+      <c r="B21" s="27" t="s">
+        <v>29</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
@@ -1376,13 +1349,11 @@
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A22" s="26"/>
-      <c r="B22" s="8" t="s">
-        <v>14</v>
-      </c>
+    <row r="22" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="30"/>
+      <c r="B22" s="28"/>
       <c r="C22" s="8" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
@@ -1400,13 +1371,11 @@
       <c r="Q22" s="7"/>
       <c r="R22" s="7"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A23" s="28"/>
-      <c r="B23" s="4" t="s">
-        <v>14</v>
-      </c>
+    <row r="23" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="33"/>
+      <c r="B23" s="29"/>
       <c r="C23" s="4" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
@@ -1424,15 +1393,15 @@
       <c r="Q23" s="5"/>
       <c r="R23" s="5"/>
     </row>
-    <row r="24" spans="1:18" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>16</v>
+    <row r="24" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="27" t="s">
+        <v>31</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
@@ -1450,13 +1419,11 @@
       <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A25" s="26"/>
-      <c r="B25" s="8" t="s">
-        <v>16</v>
-      </c>
+    <row r="25" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="30"/>
+      <c r="B25" s="28"/>
       <c r="C25" s="8" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
@@ -1474,13 +1441,11 @@
       <c r="Q25" s="7"/>
       <c r="R25" s="7"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A26" s="26"/>
-      <c r="B26" s="4" t="s">
-        <v>16</v>
-      </c>
+    <row r="26" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="30"/>
+      <c r="B26" s="29"/>
       <c r="C26" s="4" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -1498,13 +1463,13 @@
       <c r="Q26" s="5"/>
       <c r="R26" s="5"/>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A27" s="26"/>
-      <c r="B27" s="2" t="s">
-        <v>17</v>
+    <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="30"/>
+      <c r="B27" s="27" t="s">
+        <v>32</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
@@ -1522,13 +1487,11 @@
       <c r="Q27" s="3"/>
       <c r="R27" s="3"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A28" s="26"/>
-      <c r="B28" s="8" t="s">
-        <v>17</v>
-      </c>
+    <row r="28" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="30"/>
+      <c r="B28" s="28"/>
       <c r="C28" s="8" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
@@ -1546,13 +1509,11 @@
       <c r="Q28" s="7"/>
       <c r="R28" s="7"/>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A29" s="26"/>
-      <c r="B29" s="4" t="s">
-        <v>17</v>
-      </c>
+    <row r="29" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="30"/>
+      <c r="B29" s="29"/>
       <c r="C29" s="4" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5"/>
@@ -1570,13 +1531,13 @@
       <c r="Q29" s="5"/>
       <c r="R29" s="5"/>
     </row>
-    <row r="30" spans="1:18" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="26"/>
-      <c r="B30" s="2" t="s">
-        <v>18</v>
+    <row r="30" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="30"/>
+      <c r="B30" s="27" t="s">
+        <v>33</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
@@ -1594,13 +1555,11 @@
       <c r="Q30" s="3"/>
       <c r="R30" s="3"/>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A31" s="26"/>
-      <c r="B31" s="8" t="s">
-        <v>18</v>
-      </c>
+    <row r="31" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="30"/>
+      <c r="B31" s="28"/>
       <c r="C31" s="8" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
@@ -1618,13 +1577,11 @@
       <c r="Q31" s="7"/>
       <c r="R31" s="7"/>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A32" s="28"/>
-      <c r="B32" s="4" t="s">
-        <v>18</v>
-      </c>
+    <row r="32" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="33"/>
+      <c r="B32" s="29"/>
       <c r="C32" s="4" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
@@ -1642,52 +1599,55 @@
       <c r="Q32" s="5"/>
       <c r="R32" s="5"/>
     </row>
-    <row r="33" spans="1:18" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="B33" s="32"/>
-      <c r="C33" s="32"/>
-      <c r="D33" s="33"/>
-      <c r="E33" s="33"/>
-      <c r="F33" s="33"/>
-      <c r="G33" s="33"/>
-      <c r="H33" s="33"/>
-      <c r="I33" s="33"/>
-      <c r="J33" s="33"/>
-      <c r="K33" s="33"/>
-      <c r="L33" s="33"/>
-      <c r="M33" s="33"/>
-      <c r="N33" s="33"/>
-      <c r="O33" s="33"/>
-      <c r="P33" s="33"/>
-      <c r="Q33" s="33"/>
-      <c r="R33" s="33"/>
-    </row>
-    <row r="34" spans="1:18" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="B34" s="35"/>
-      <c r="C34" s="35"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="36"/>
-      <c r="I34" s="36"/>
-      <c r="J34" s="36"/>
-      <c r="K34" s="36"/>
-      <c r="L34" s="36"/>
-      <c r="M34" s="36"/>
-      <c r="N34" s="36"/>
-      <c r="O34" s="36"/>
-      <c r="P34" s="36"/>
-      <c r="Q34" s="36"/>
-      <c r="R34" s="36"/>
+    <row r="33" spans="1:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="B33" s="35"/>
+      <c r="C33" s="35"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="26"/>
+      <c r="J33" s="26"/>
+      <c r="K33" s="26"/>
+      <c r="L33" s="26"/>
+      <c r="M33" s="26"/>
+      <c r="N33" s="26"/>
+      <c r="O33" s="26"/>
+      <c r="P33" s="26"/>
+      <c r="Q33" s="26"/>
+      <c r="R33" s="26"/>
+    </row>
+    <row r="34" spans="1:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="25"/>
+      <c r="J34" s="25"/>
+      <c r="K34" s="25"/>
+      <c r="L34" s="25"/>
+      <c r="M34" s="25"/>
+      <c r="N34" s="25"/>
+      <c r="O34" s="25"/>
+      <c r="P34" s="25"/>
+      <c r="Q34" s="25"/>
+      <c r="R34" s="25"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="17">
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="B30:B32"/>
     <mergeCell ref="A34:C34"/>
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A33:C33"/>
@@ -1695,6 +1655,13 @@
     <mergeCell ref="A6:A14"/>
     <mergeCell ref="A15:A23"/>
     <mergeCell ref="A24:A32"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="B21:B23"/>
   </mergeCells>
   <conditionalFormatting sqref="D3:R3">
     <cfRule type="top10" dxfId="13" priority="10" bottom="1" rank="1"/>
@@ -1733,82 +1700,82 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.109375" customWidth="1"/>
-    <col min="2" max="9" width="15.109375" customWidth="1"/>
-    <col min="10" max="15" width="16.109375" customWidth="1"/>
+    <col min="1" max="1" width="8.140625" customWidth="1"/>
+    <col min="2" max="9" width="15.140625" customWidth="1"/>
+    <col min="10" max="15" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="C2" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="D2" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="E2" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="F2" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="G2" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="H2" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="I2" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="J2" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="K2" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="L2" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="K2" s="16" t="s">
+      <c r="M2" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="L2" s="16" t="s">
+      <c r="N2" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="M2" s="16" t="s">
+      <c r="O2" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="N2" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="O2" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1825,9 +1792,9 @@
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -1844,9 +1811,9 @@
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1863,9 +1830,9 @@
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -1882,9 +1849,9 @@
       <c r="N6" s="7"/>
       <c r="O6" s="7"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -1901,9 +1868,9 @@
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -1920,9 +1887,9 @@
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -1939,9 +1906,9 @@
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -1958,9 +1925,9 @@
       <c r="N10" s="7"/>
       <c r="O10" s="7"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -1977,9 +1944,9 @@
       <c r="N11" s="7"/>
       <c r="O11" s="7"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -2012,82 +1979,82 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" customWidth="1"/>
-    <col min="2" max="9" width="15.109375" customWidth="1"/>
-    <col min="10" max="15" width="16.109375" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" customWidth="1"/>
+    <col min="2" max="9" width="15.140625" customWidth="1"/>
+    <col min="10" max="15" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="D2" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="E2" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="F2" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="G2" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="H2" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="I2" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="J2" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="K2" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="L2" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="K2" s="16" t="s">
+      <c r="M2" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="L2" s="16" t="s">
+      <c r="N2" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="M2" s="16" t="s">
+      <c r="O2" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="N2" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="O2" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -2104,9 +2071,9 @@
       <c r="N3" s="13"/>
       <c r="O3" s="13"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
@@ -2123,9 +2090,9 @@
       <c r="N4" s="14"/>
       <c r="O4" s="14"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B5" s="14"/>
       <c r="C5" s="14"/>
@@ -2142,9 +2109,9 @@
       <c r="N5" s="14"/>
       <c r="O5" s="14"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B6" s="14"/>
       <c r="C6" s="14"/>
@@ -2161,9 +2128,9 @@
       <c r="N6" s="14"/>
       <c r="O6" s="14"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B7" s="14"/>
       <c r="C7" s="14"/>
@@ -2180,9 +2147,9 @@
       <c r="N7" s="14"/>
       <c r="O7" s="14"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
@@ -2199,9 +2166,9 @@
       <c r="N8" s="14"/>
       <c r="O8" s="14"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B9" s="14"/>
       <c r="C9" s="14"/>
@@ -2218,9 +2185,9 @@
       <c r="N9" s="14"/>
       <c r="O9" s="14"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
@@ -2237,9 +2204,9 @@
       <c r="N10" s="14"/>
       <c r="O10" s="14"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
@@ -2256,9 +2223,9 @@
       <c r="N11" s="14"/>
       <c r="O11" s="14"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B12" s="15"/>
       <c r="C12" s="15"/>
@@ -2291,82 +2258,82 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:O12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" customWidth="1"/>
-    <col min="2" max="9" width="15.109375" customWidth="1"/>
-    <col min="10" max="15" width="16.109375" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" customWidth="1"/>
+    <col min="2" max="9" width="15.140625" customWidth="1"/>
+    <col min="10" max="15" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
-        <v>53</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="D2" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="E2" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="F2" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="G2" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="H2" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="I2" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="J2" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="K2" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="L2" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="K2" s="16" t="s">
+      <c r="M2" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="L2" s="16" t="s">
+      <c r="N2" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="M2" s="16" t="s">
+      <c r="O2" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="N2" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="O2" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -2383,9 +2350,9 @@
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -2402,9 +2369,9 @@
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -2421,9 +2388,9 @@
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -2440,9 +2407,9 @@
       <c r="N6" s="7"/>
       <c r="O6" s="7"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -2459,9 +2426,9 @@
       <c r="N7" s="7"/>
       <c r="O7" s="7"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -2478,9 +2445,9 @@
       <c r="N8" s="7"/>
       <c r="O8" s="7"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -2497,9 +2464,9 @@
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -2516,9 +2483,9 @@
       <c r="N10" s="7"/>
       <c r="O10" s="7"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -2535,9 +2502,9 @@
       <c r="N11" s="7"/>
       <c r="O11" s="7"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -2570,82 +2537,82 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:O12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" customWidth="1"/>
-    <col min="2" max="9" width="15.109375" customWidth="1"/>
-    <col min="10" max="15" width="16.109375" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" customWidth="1"/>
+    <col min="2" max="9" width="15.140625" customWidth="1"/>
+    <col min="10" max="15" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="D2" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="E2" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="F2" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="G2" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="H2" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="I2" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="J2" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="K2" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="L2" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="K2" s="16" t="s">
+      <c r="M2" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="L2" s="16" t="s">
+      <c r="N2" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="M2" s="16" t="s">
+      <c r="O2" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="N2" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="O2" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -2662,9 +2629,9 @@
       <c r="N3" s="13"/>
       <c r="O3" s="13"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
@@ -2681,9 +2648,9 @@
       <c r="N4" s="14"/>
       <c r="O4" s="14"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B5" s="14"/>
       <c r="C5" s="14"/>
@@ -2700,9 +2667,9 @@
       <c r="N5" s="14"/>
       <c r="O5" s="14"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B6" s="14"/>
       <c r="C6" s="14"/>
@@ -2719,9 +2686,9 @@
       <c r="N6" s="14"/>
       <c r="O6" s="14"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B7" s="14"/>
       <c r="C7" s="14"/>
@@ -2738,9 +2705,9 @@
       <c r="N7" s="14"/>
       <c r="O7" s="14"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
@@ -2757,9 +2724,9 @@
       <c r="N8" s="14"/>
       <c r="O8" s="14"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B9" s="14"/>
       <c r="C9" s="14"/>
@@ -2776,9 +2743,9 @@
       <c r="N9" s="14"/>
       <c r="O9" s="14"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
@@ -2795,9 +2762,9 @@
       <c r="N10" s="14"/>
       <c r="O10" s="14"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
@@ -2814,9 +2781,9 @@
       <c r="N11" s="14"/>
       <c r="O11" s="14"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B12" s="15"/>
       <c r="C12" s="15"/>
@@ -2849,83 +2816,83 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:O12"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="6" customWidth="1"/>
-    <col min="2" max="9" width="15.109375" style="6" customWidth="1"/>
-    <col min="10" max="15" width="16.109375" style="6" customWidth="1"/>
-    <col min="16" max="16384" width="8.88671875" style="6"/>
+    <col min="1" max="1" width="8.7109375" style="6" customWidth="1"/>
+    <col min="2" max="9" width="15.140625" style="6" customWidth="1"/>
+    <col min="10" max="15" width="16.140625" style="6" customWidth="1"/>
+    <col min="16" max="16384" width="8.85546875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="D2" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="E2" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="F2" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="G2" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="H2" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="I2" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="J2" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="K2" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="L2" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="K2" s="16" t="s">
+      <c r="M2" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="L2" s="16" t="s">
+      <c r="N2" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="M2" s="16" t="s">
+      <c r="O2" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="N2" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="O2" s="16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -2942,9 +2909,9 @@
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -2961,9 +2928,9 @@
       <c r="N4" s="8"/>
       <c r="O4" s="8"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -2980,9 +2947,9 @@
       <c r="N5" s="8"/>
       <c r="O5" s="8"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2999,9 +2966,9 @@
       <c r="N6" s="8"/>
       <c r="O6" s="8"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -3018,9 +2985,9 @@
       <c r="N7" s="8"/>
       <c r="O7" s="8"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -3037,9 +3004,9 @@
       <c r="N8" s="8"/>
       <c r="O8" s="8"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -3056,9 +3023,9 @@
       <c r="N9" s="8"/>
       <c r="O9" s="8"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -3075,9 +3042,9 @@
       <c r="N10" s="8"/>
       <c r="O10" s="8"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -3094,9 +3061,9 @@
       <c r="N11" s="8"/>
       <c r="O11" s="8"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -3124,100 +3091,102 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:S25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="16" width="15" customWidth="1"/>
-    <col min="17" max="17" width="20" customWidth="1"/>
-    <col min="18" max="18" width="18" customWidth="1"/>
-    <col min="19" max="19" width="14" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="10" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="17"/>
-      <c r="S1" s="17"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2" s="17" t="s">
+      <c r="D2" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="E2" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="F2" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="G2" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="H2" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="I2" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="J2" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="K2" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="L2" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="K2" s="17" t="s">
+      <c r="M2" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="L2" s="17" t="s">
+      <c r="N2" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="M2" s="17" t="s">
+      <c r="O2" s="37" t="s">
         <v>68</v>
       </c>
-      <c r="N2" s="17" t="s">
+      <c r="P2" s="37" t="s">
         <v>69</v>
       </c>
-      <c r="O2" s="17" t="s">
+      <c r="Q2" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="P2" s="17" t="s">
+      <c r="R2" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="17" t="s">
+      <c r="S2" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="R2" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="S2" s="17" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -3238,9 +3207,9 @@
       <c r="R3" s="17"/>
       <c r="S3" s="17"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -3261,9 +3230,9 @@
       <c r="R4" s="17"/>
       <c r="S4" s="17"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B5" s="17"/>
       <c r="C5" s="17"/>
@@ -3284,9 +3253,9 @@
       <c r="R5" s="17"/>
       <c r="S5" s="17"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
@@ -3307,9 +3276,9 @@
       <c r="R6" s="17"/>
       <c r="S6" s="17"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
@@ -3330,9 +3299,9 @@
       <c r="R7" s="17"/>
       <c r="S7" s="17"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
@@ -3353,9 +3322,9 @@
       <c r="R8" s="17"/>
       <c r="S8" s="17"/>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="17"/>
@@ -3376,9 +3345,9 @@
       <c r="R9" s="17"/>
       <c r="S9" s="17"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
@@ -3399,9 +3368,9 @@
       <c r="R10" s="17"/>
       <c r="S10" s="17"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B11" s="17"/>
       <c r="C11" s="17"/>
@@ -3422,9 +3391,9 @@
       <c r="R11" s="17"/>
       <c r="S11" s="17"/>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
@@ -3445,7 +3414,7 @@
       <c r="R12" s="17"/>
       <c r="S12" s="17"/>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="17"/>
       <c r="B13" s="17"/>
       <c r="C13" s="17"/>
@@ -3466,53 +3435,53 @@
       <c r="R13" s="17"/>
       <c r="S13" s="17"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A14" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="19"/>
-      <c r="K14" s="19"/>
-      <c r="L14" s="19"/>
-      <c r="M14" s="19"/>
-      <c r="N14" s="19"/>
-      <c r="O14" s="19"/>
-      <c r="P14" s="19"/>
-      <c r="Q14" s="19"/>
-      <c r="R14" s="19"/>
-      <c r="S14" s="19"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A15" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-      <c r="M15" s="20"/>
-      <c r="N15" s="20"/>
-      <c r="O15" s="20"/>
-      <c r="P15" s="20"/>
-      <c r="Q15" s="20"/>
-      <c r="R15" s="20"/>
-      <c r="S15" s="20"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="18"/>
+      <c r="K14" s="18"/>
+      <c r="L14" s="18"/>
+      <c r="M14" s="18"/>
+      <c r="N14" s="18"/>
+      <c r="O14" s="18"/>
+      <c r="P14" s="18"/>
+      <c r="Q14" s="18"/>
+      <c r="R14" s="18"/>
+      <c r="S14" s="18"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="19"/>
+      <c r="M15" s="19"/>
+      <c r="N15" s="19"/>
+      <c r="O15" s="19"/>
+      <c r="P15" s="19"/>
+      <c r="Q15" s="19"/>
+      <c r="R15" s="19"/>
+      <c r="S15" s="19"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="17"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17"/>
@@ -3533,32 +3502,32 @@
       <c r="R16" s="17"/>
       <c r="S16" s="17"/>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A17" s="21" t="s">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="20"/>
+      <c r="R17" s="20"/>
+      <c r="S17" s="20"/>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="s">
         <v>76</v>
-      </c>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="21"/>
-      <c r="K17" s="21"/>
-      <c r="L17" s="21"/>
-      <c r="M17" s="21"/>
-      <c r="N17" s="21"/>
-      <c r="O17" s="21"/>
-      <c r="P17" s="21"/>
-      <c r="Q17" s="21"/>
-      <c r="R17" s="21"/>
-      <c r="S17" s="21"/>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A18" s="17" t="s">
-        <v>77</v>
       </c>
       <c r="B18" s="17"/>
       <c r="C18" s="17"/>
@@ -3579,9 +3548,9 @@
       <c r="R18" s="17"/>
       <c r="S18" s="17"/>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
@@ -3602,9 +3571,9 @@
       <c r="R19" s="17"/>
       <c r="S19" s="17"/>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B20" s="17"/>
       <c r="C20" s="17"/>
@@ -3625,7 +3594,7 @@
       <c r="R20" s="17"/>
       <c r="S20" s="17"/>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="17"/>
       <c r="B21" s="17"/>
       <c r="C21" s="17"/>
@@ -3646,18 +3615,18 @@
       <c r="R21" s="17"/>
       <c r="S21" s="17"/>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A22" s="21" t="s">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A22" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="C22" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="D22" s="20" t="s">
         <v>80</v>
-      </c>
-      <c r="C22" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="D22" s="21" t="s">
-        <v>81</v>
       </c>
       <c r="E22" s="17"/>
       <c r="F22" s="17"/>
@@ -3675,7 +3644,7 @@
       <c r="R22" s="17"/>
       <c r="S22" s="17"/>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="17"/>
       <c r="B23" s="17"/>
       <c r="C23" s="17"/>
@@ -3696,7 +3665,7 @@
       <c r="R23" s="17"/>
       <c r="S23" s="17"/>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="17"/>
       <c r="B24" s="17"/>
       <c r="C24" s="17"/>
@@ -3717,7 +3686,7 @@
       <c r="R24" s="17"/>
       <c r="S24" s="17"/>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="17"/>
       <c r="B25" s="17"/>
       <c r="C25" s="17"/>
@@ -3739,6 +3708,9 @@
       <c r="S25" s="17"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:S1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3746,82 +3718,82 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="95" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:2" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="23" t="s">
+    </row>
+    <row r="2" spans="1:2" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="21" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+      <c r="B2" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="23" t="s">
+    </row>
+    <row r="3" spans="1:2" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="22" t="s">
+      <c r="B3" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="B3" s="23" t="s">
+    </row>
+    <row r="4" spans="1:2" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="22" t="s">
+      <c r="B4" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="B4" s="23" t="s">
+    </row>
+    <row r="5" spans="1:2" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="21" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="22" t="s">
+      <c r="B5" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="B5" s="23" t="s">
+    </row>
+    <row r="6" spans="1:2" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="21" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="22" t="s">
+      <c r="B6" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="B6" s="23" t="s">
+    </row>
+    <row r="7" spans="1:2" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="22" t="s">
+      <c r="B7" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="B7" s="23" t="s">
+    </row>
+    <row r="8" spans="1:2" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="22" t="s">
+      <c r="B8" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="B8" s="23" t="s">
+    </row>
+    <row r="9" spans="1:2" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="23" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="24" t="s">
+      <c r="B9" s="24" t="s">
         <v>98</v>
-      </c>
-      <c r="B9" s="25" t="s">
-        <v>99</v>
       </c>
     </row>
   </sheetData>
